--- a/q2_test/outputs/q2/result2.xlsx
+++ b/q2_test/outputs/q2/result2.xlsx
@@ -1082,10 +1082,10 @@
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8" t="n">
+      <c r="C2" s="8" t="n">
         <v>80</v>
       </c>
+      <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
@@ -1132,13 +1132,13 @@
       <c r="B3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="C3" s="9"/>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
+      <c r="G3" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -1183,11 +1183,11 @@
         <v>2</v>
       </c>
       <c r="C4" s="8"/>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
@@ -1242,13 +1242,13 @@
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
-      <c r="M5" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
+      <c r="Q5" s="9" t="n">
+        <v>72</v>
+      </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
@@ -1287,9 +1287,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="8" t="n">
-        <v>68</v>
-      </c>
+      <c r="H6" s="8"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
@@ -1297,7 +1295,9 @@
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="P6" s="8" t="n">
+        <v>68</v>
+      </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
@@ -1438,13 +1438,13 @@
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="I9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
+      <c r="M9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
@@ -1485,15 +1485,15 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
-      <c r="F10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="L10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
@@ -1533,14 +1533,14 @@
         <v>9</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="9" t="n">
-        <v>28</v>
-      </c>
+      <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="I11" s="9" t="n">
+        <v>28</v>
+      </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -1582,14 +1582,14 @@
       <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="8" t="n">
-        <v>25</v>
-      </c>
+      <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="H12" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
@@ -1633,11 +1633,11 @@
         <v>11</v>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -1682,11 +1682,11 @@
       <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
@@ -1888,13 +1888,13 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
-      <c r="I18" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
+      <c r="M18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -1932,10 +1932,10 @@
       <c r="B19" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="9"/>
+      <c r="D19" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
@@ -1982,12 +1982,12 @@
       <c r="B20" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="8"/>
+      <c r="C20" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
@@ -2033,10 +2033,10 @@
         <v>19</v>
       </c>
       <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9" t="n">
+      <c r="D21" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
@@ -2082,10 +2082,10 @@
       <c r="B22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8" t="n">
+      <c r="C22" s="8" t="n">
         <v>15</v>
       </c>
+      <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
@@ -2132,11 +2132,11 @@
       <c r="B23" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
@@ -2184,7 +2184,9 @@
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="E24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -2193,9 +2195,7 @@
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
-      <c r="N24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="N24" s="8"/>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
@@ -2338,15 +2338,15 @@
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
+      <c r="O27" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2402,13 +2402,13 @@
       <c r="T28" s="8"/>
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
-      <c r="W28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="W28" s="8"/>
       <c r="X28" s="8"/>
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
-      <c r="AA28" s="8"/>
+      <c r="AA28" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="AB28" s="8"/>
       <c r="AC28" s="8"/>
       <c r="AD28" s="8"/>
@@ -2449,7 +2449,9 @@
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
+      <c r="T29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="U29" s="9"/>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -2458,9 +2460,7 @@
       <c r="Z29" s="9"/>
       <c r="AA29" s="9"/>
       <c r="AB29" s="9"/>
-      <c r="AC29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="AC29" s="9"/>
       <c r="AD29" s="9"/>
       <c r="AE29" s="9"/>
       <c r="AF29" s="9"/>
@@ -2501,13 +2501,13 @@
       <c r="S30" s="8"/>
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
-      <c r="V30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="V30" s="8"/>
       <c r="W30" s="8"/>
       <c r="X30" s="8"/>
       <c r="Y30" s="8"/>
-      <c r="Z30" s="8"/>
+      <c r="Z30" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
       <c r="AC30" s="8"/>
@@ -2548,16 +2548,16 @@
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
+      <c r="S31" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="T31" s="9"/>
       <c r="U31" s="9"/>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
       <c r="X31" s="9"/>
       <c r="Y31" s="9"/>
-      <c r="Z31" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="Z31" s="9"/>
       <c r="AA31" s="9"/>
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
@@ -2598,13 +2598,13 @@
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
-      <c r="S32" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="S32" s="8"/>
       <c r="T32" s="8"/>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
-      <c r="W32" s="8"/>
+      <c r="W32" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="X32" s="8"/>
       <c r="Y32" s="8"/>
       <c r="Z32" s="8"/>
@@ -2654,13 +2654,13 @@
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
       <c r="X33" s="9"/>
-      <c r="Y33" s="9" t="n">
-        <v>12</v>
-      </c>
+      <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
       <c r="AA33" s="9"/>
       <c r="AB33" s="9"/>
-      <c r="AC33" s="9"/>
+      <c r="AC33" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="AD33" s="9"/>
       <c r="AE33" s="9"/>
       <c r="AF33" s="9"/>
@@ -2698,7 +2698,9 @@
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
+      <c r="S34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="T34" s="8"/>
       <c r="U34" s="8"/>
       <c r="V34" s="8"/>
@@ -2710,9 +2712,7 @@
       <c r="AB34" s="8"/>
       <c r="AC34" s="8"/>
       <c r="AD34" s="8"/>
-      <c r="AE34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="AE34" s="8"/>
       <c r="AF34" s="8"/>
       <c r="AG34" s="8"/>
       <c r="AH34" s="8"/>
@@ -2798,7 +2798,9 @@
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
       <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
+      <c r="S36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T36" s="8"/>
       <c r="U36" s="8"/>
       <c r="V36" s="8"/>
@@ -2807,9 +2809,7 @@
       <c r="Y36" s="8"/>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
-      <c r="AB36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB36" s="8"/>
       <c r="AC36" s="8"/>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
@@ -2848,13 +2848,13 @@
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
-      <c r="S37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S37" s="9"/>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
       <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
+      <c r="W37" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
@@ -2902,13 +2902,13 @@
       <c r="T38" s="8"/>
       <c r="U38" s="8"/>
       <c r="V38" s="8"/>
-      <c r="W38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="W38" s="8"/>
       <c r="X38" s="8"/>
       <c r="Y38" s="8"/>
       <c r="Z38" s="8"/>
-      <c r="AA38" s="8"/>
+      <c r="AA38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AB38" s="8"/>
       <c r="AC38" s="8"/>
       <c r="AD38" s="8"/>
@@ -2954,15 +2954,15 @@
       <c r="V39" s="9"/>
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
-      <c r="Y39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
       <c r="AA39" s="9"/>
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="9"/>
-      <c r="AE39" s="9"/>
+      <c r="AE39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF39" s="9"/>
       <c r="AG39" s="9"/>
       <c r="AH39" s="9"/>
@@ -2999,7 +2999,9 @@
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
       <c r="S40" s="8"/>
-      <c r="T40" s="8"/>
+      <c r="T40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U40" s="8"/>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
@@ -3008,9 +3010,7 @@
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
       <c r="AB40" s="8"/>
-      <c r="AC40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AC40" s="8"/>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
       <c r="AF40" s="8"/>
@@ -3049,13 +3049,13 @@
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
-      <c r="T41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T41" s="9"/>
       <c r="U41" s="9"/>
       <c r="V41" s="9"/>
       <c r="W41" s="9"/>
-      <c r="X41" s="9"/>
+      <c r="X41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
       <c r="AA41" s="9"/>
@@ -3107,16 +3107,16 @@
       <c r="Y42" s="8"/>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
+      <c r="AB42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AC42" s="8"/>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8"/>
       <c r="AF42" s="8"/>
       <c r="AG42" s="8"/>
       <c r="AH42" s="8"/>
-      <c r="AI42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AI42" s="8"/>
       <c r="AJ42" s="8"/>
       <c r="AK42" s="8"/>
       <c r="AL42" s="8"/>
@@ -3155,13 +3155,13 @@
       <c r="W43" s="9"/>
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
-      <c r="Z43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Z43" s="9"/>
       <c r="AA43" s="9"/>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
-      <c r="AD43" s="9"/>
+      <c r="AD43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AE43" s="9"/>
       <c r="AF43" s="9"/>
       <c r="AG43" s="9"/>
@@ -3200,7 +3200,9 @@
       <c r="R44" s="8"/>
       <c r="S44" s="8"/>
       <c r="T44" s="8"/>
-      <c r="U44" s="8"/>
+      <c r="U44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
@@ -3209,9 +3211,7 @@
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
       <c r="AC44" s="8"/>
-      <c r="AD44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD44" s="8"/>
       <c r="AE44" s="8"/>
       <c r="AF44" s="8"/>
       <c r="AG44" s="8"/>
@@ -3250,13 +3250,13 @@
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
       <c r="T45" s="9"/>
-      <c r="U45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U45" s="9"/>
       <c r="V45" s="9"/>
       <c r="W45" s="9"/>
       <c r="X45" s="9"/>
-      <c r="Y45" s="9"/>
+      <c r="Y45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Z45" s="9"/>
       <c r="AA45" s="9"/>
       <c r="AB45" s="9"/>
@@ -3302,15 +3302,15 @@
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
       <c r="V46" s="8"/>
-      <c r="W46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="W46" s="8"/>
       <c r="X46" s="8"/>
       <c r="Y46" s="8"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
       <c r="AF46" s="8"/>
@@ -3348,7 +3348,9 @@
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
-      <c r="S47" s="9"/>
+      <c r="S47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T47" s="9"/>
       <c r="U47" s="9"/>
       <c r="V47" s="9"/>
@@ -3356,9 +3358,7 @@
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
       <c r="Z47" s="9"/>
-      <c r="AA47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AA47" s="9"/>
       <c r="AB47" s="9"/>
       <c r="AC47" s="9"/>
       <c r="AD47" s="9"/>
@@ -3400,10 +3400,10 @@
       <c r="R48" s="8"/>
       <c r="S48" s="8"/>
       <c r="T48" s="8"/>
-      <c r="U48" s="8" t="n">
+      <c r="U48" s="8"/>
+      <c r="V48" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="V48" s="8"/>
       <c r="W48" s="8"/>
       <c r="X48" s="8"/>
       <c r="Y48" s="8"/>
@@ -3455,16 +3455,16 @@
       <c r="W49" s="9"/>
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
-      <c r="Z49" s="9"/>
+      <c r="Z49" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AA49" s="9"/>
       <c r="AB49" s="9"/>
       <c r="AC49" s="9"/>
       <c r="AD49" s="9"/>
       <c r="AE49" s="9"/>
       <c r="AF49" s="9"/>
-      <c r="AG49" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AG49" s="9"/>
       <c r="AH49" s="9"/>
       <c r="AI49" s="9"/>
       <c r="AJ49" s="9"/>
@@ -3503,13 +3503,13 @@
       <c r="U50" s="8"/>
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
-      <c r="X50" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X50" s="8"/>
       <c r="Y50" s="8"/>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
+      <c r="AB50" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AC50" s="8"/>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
@@ -3548,7 +3548,9 @@
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
-      <c r="S51" s="9"/>
+      <c r="S51" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T51" s="9"/>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
@@ -3557,9 +3559,7 @@
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
       <c r="AA51" s="9"/>
-      <c r="AB51" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB51" s="9"/>
       <c r="AC51" s="9"/>
       <c r="AD51" s="9"/>
       <c r="AE51" s="9"/>
@@ -3598,11 +3598,11 @@
       <c r="P52" s="8"/>
       <c r="Q52" s="8"/>
       <c r="R52" s="8"/>
-      <c r="S52" s="8" t="n">
+      <c r="S52" s="8"/>
+      <c r="T52" s="8"/>
+      <c r="U52" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="T52" s="8"/>
-      <c r="U52" s="8"/>
       <c r="V52" s="8"/>
       <c r="W52" s="8"/>
       <c r="X52" s="8"/>
@@ -3648,15 +3648,15 @@
       <c r="P53" s="9"/>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
+      <c r="S53" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T53" s="9"/>
       <c r="U53" s="9"/>
       <c r="V53" s="9"/>
       <c r="W53" s="9"/>
       <c r="X53" s="9"/>
-      <c r="Y53" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
       <c r="AA53" s="9"/>
       <c r="AB53" s="9"/>
@@ -3698,15 +3698,15 @@
       <c r="P54" s="8"/>
       <c r="Q54" s="8"/>
       <c r="R54" s="8"/>
-      <c r="S54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S54" s="8"/>
       <c r="T54" s="8"/>
       <c r="U54" s="8"/>
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
-      <c r="Y54" s="8"/>
+      <c r="Y54" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
       <c r="AB54" s="8"/>
@@ -3748,11 +3748,11 @@
       <c r="P55" s="9"/>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
-      <c r="S55" s="9" t="n">
+      <c r="S55" s="9"/>
+      <c r="T55" s="9"/>
+      <c r="U55" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
       <c r="V55" s="9"/>
       <c r="W55" s="9"/>
       <c r="X55" s="9"/>
@@ -4161,10 +4161,10 @@
       <c r="AH63" s="9"/>
       <c r="AI63" s="9"/>
       <c r="AJ63" s="9"/>
-      <c r="AK63" s="9"/>
-      <c r="AL63" s="9" t="n">
+      <c r="AK63" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="AL63" s="9"/>
       <c r="AM63" s="9"/>
       <c r="AN63" s="9"/>
       <c r="AO63" s="9"/>
@@ -4213,10 +4213,10 @@
       <c r="AK64" s="8"/>
       <c r="AL64" s="8"/>
       <c r="AM64" s="8"/>
-      <c r="AN64" s="8"/>
-      <c r="AO64" s="8" t="n">
+      <c r="AN64" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO64" s="8"/>
       <c r="AP64" s="8"/>
       <c r="AQ64" s="8"/>
     </row>
@@ -4263,11 +4263,11 @@
       <c r="AL65" s="9"/>
       <c r="AM65" s="9"/>
       <c r="AN65" s="9"/>
-      <c r="AO65" s="9" t="n">
+      <c r="AO65" s="9"/>
+      <c r="AP65" s="9"/>
+      <c r="AQ65" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP65" s="9"/>
-      <c r="AQ65" s="9"/>
     </row>
     <row r="66" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A66" s="18"/>
@@ -4311,10 +4311,10 @@
       <c r="AK66" s="8"/>
       <c r="AL66" s="8"/>
       <c r="AM66" s="8"/>
-      <c r="AN66" s="8"/>
-      <c r="AO66" s="8" t="n">
+      <c r="AN66" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO66" s="8"/>
       <c r="AP66" s="8"/>
       <c r="AQ66" s="8"/>
     </row>
@@ -4361,11 +4361,11 @@
       <c r="AL67" s="9"/>
       <c r="AM67" s="9"/>
       <c r="AN67" s="9"/>
-      <c r="AO67" s="9" t="n">
+      <c r="AO67" s="9"/>
+      <c r="AP67" s="9"/>
+      <c r="AQ67" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP67" s="9"/>
-      <c r="AQ67" s="9"/>
     </row>
     <row r="68" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A68" s="18"/>
@@ -4409,11 +4409,11 @@
       <c r="AK68" s="8"/>
       <c r="AL68" s="8"/>
       <c r="AM68" s="8"/>
-      <c r="AN68" s="8" t="n">
+      <c r="AN68" s="8"/>
+      <c r="AO68" s="8"/>
+      <c r="AP68" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO68" s="8"/>
-      <c r="AP68" s="8"/>
       <c r="AQ68" s="8"/>
     </row>
     <row r="69" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -4509,10 +4509,10 @@
       <c r="AM70" s="8"/>
       <c r="AN70" s="8"/>
       <c r="AO70" s="8"/>
-      <c r="AP70" s="8" t="n">
+      <c r="AP70" s="8"/>
+      <c r="AQ70" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AQ70" s="8"/>
     </row>
     <row r="71" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
       <c r="A71" s="18"/>
@@ -4557,10 +4557,10 @@
       <c r="AL71" s="9"/>
       <c r="AM71" s="9"/>
       <c r="AN71" s="9"/>
-      <c r="AO71" s="9"/>
-      <c r="AP71" s="9" t="n">
+      <c r="AO71" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP71" s="9"/>
       <c r="AQ71" s="9"/>
     </row>
     <row r="72" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -4606,11 +4606,11 @@
       <c r="AL72" s="8"/>
       <c r="AM72" s="8"/>
       <c r="AN72" s="8"/>
-      <c r="AO72" s="8"/>
+      <c r="AO72" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP72" s="8"/>
-      <c r="AQ72" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ72" s="8"/>
     </row>
     <row r="73" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
       <c r="A73" s="18"/>
@@ -4704,11 +4704,11 @@
       <c r="AL74" s="8"/>
       <c r="AM74" s="8"/>
       <c r="AN74" s="8"/>
-      <c r="AO74" s="8" t="n">
+      <c r="AO74" s="8"/>
+      <c r="AP74" s="8"/>
+      <c r="AQ74" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP74" s="8"/>
-      <c r="AQ74" s="8"/>
     </row>
     <row r="75" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
       <c r="A75" s="18"/>
@@ -4752,12 +4752,12 @@
       <c r="AK75" s="9"/>
       <c r="AL75" s="9"/>
       <c r="AM75" s="9"/>
-      <c r="AN75" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AN75" s="9"/>
       <c r="AO75" s="9"/>
       <c r="AP75" s="9"/>
-      <c r="AQ75" s="9"/>
+      <c r="AQ75" s="9" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="76" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A76" s="18"/>
@@ -4802,11 +4802,11 @@
       <c r="AL76" s="8"/>
       <c r="AM76" s="8"/>
       <c r="AN76" s="8"/>
-      <c r="AO76" s="8" t="n">
+      <c r="AO76" s="8"/>
+      <c r="AP76" s="8"/>
+      <c r="AQ76" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP76" s="8"/>
-      <c r="AQ76" s="8"/>
     </row>
     <row r="77" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
       <c r="A77" s="18"/>
@@ -4850,10 +4850,10 @@
       <c r="AK77" s="9"/>
       <c r="AL77" s="9"/>
       <c r="AM77" s="9"/>
-      <c r="AN77" s="9"/>
-      <c r="AO77" s="9" t="n">
+      <c r="AN77" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO77" s="9"/>
       <c r="AP77" s="9"/>
       <c r="AQ77" s="9"/>
     </row>
@@ -4949,10 +4949,10 @@
       <c r="AL79" s="9"/>
       <c r="AM79" s="9"/>
       <c r="AN79" s="9"/>
-      <c r="AO79" s="9" t="n">
+      <c r="AO79" s="9"/>
+      <c r="AP79" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP79" s="9"/>
       <c r="AQ79" s="9"/>
     </row>
     <row r="80" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -4980,12 +4980,12 @@
       <c r="T80" s="8"/>
       <c r="U80" s="8"/>
       <c r="V80" s="8"/>
-      <c r="W80" s="8"/>
+      <c r="W80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="X80" s="8"/>
       <c r="Y80" s="8"/>
-      <c r="Z80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Z80" s="8"/>
       <c r="AA80" s="8"/>
       <c r="AB80" s="8"/>
       <c r="AC80" s="8"/>
@@ -6225,13 +6225,13 @@
       <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="8"/>
+      <c r="C18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
-      <c r="G18" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
@@ -6677,15 +6677,15 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="E27" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
-      <c r="K27" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
@@ -6841,10 +6841,10 @@
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="8" t="n">
+      <c r="S30" s="8" t="n">
         <v>14</v>
       </c>
+      <c r="T30" s="8"/>
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
@@ -6943,13 +6943,13 @@
       <c r="R32" s="8"/>
       <c r="S32" s="8"/>
       <c r="T32" s="8"/>
-      <c r="U32" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="8"/>
       <c r="X32" s="8"/>
-      <c r="Y32" s="8"/>
+      <c r="Y32" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8"/>
       <c r="AB32" s="8"/>
@@ -6992,16 +6992,16 @@
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
+      <c r="T33" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="U33" s="9"/>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
       <c r="X33" s="9"/>
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
-      <c r="AA33" s="9" t="n">
-        <v>12</v>
-      </c>
+      <c r="AA33" s="9"/>
       <c r="AB33" s="9"/>
       <c r="AC33" s="9"/>
       <c r="AD33" s="9"/>
@@ -7042,13 +7042,13 @@
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
       <c r="S34" s="8"/>
-      <c r="T34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="T34" s="8"/>
       <c r="U34" s="8"/>
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
-      <c r="X34" s="8"/>
+      <c r="X34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="Y34" s="8"/>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
@@ -7096,15 +7096,15 @@
       <c r="U35" s="9"/>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
-      <c r="X35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="X35" s="9"/>
       <c r="Y35" s="9"/>
       <c r="Z35" s="9"/>
       <c r="AA35" s="9"/>
       <c r="AB35" s="9"/>
       <c r="AC35" s="9"/>
-      <c r="AD35" s="9"/>
+      <c r="AD35" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="AE35" s="9"/>
       <c r="AF35" s="9"/>
       <c r="AG35" s="9"/>
@@ -7143,7 +7143,9 @@
       <c r="R36" s="8"/>
       <c r="S36" s="8"/>
       <c r="T36" s="8"/>
-      <c r="U36" s="8"/>
+      <c r="U36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
@@ -7152,9 +7154,7 @@
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
       <c r="AF36" s="8"/>
       <c r="AG36" s="8"/>
@@ -7191,10 +7191,10 @@
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
-      <c r="S37" s="9" t="n">
+      <c r="S37" s="9"/>
+      <c r="T37" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="T37" s="9"/>
       <c r="U37" s="9"/>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -7241,10 +7241,10 @@
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
       <c r="R38" s="8"/>
-      <c r="S38" s="8" t="n">
+      <c r="S38" s="8"/>
+      <c r="T38" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="T38" s="8"/>
       <c r="U38" s="8"/>
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
@@ -7342,11 +7342,11 @@
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
       <c r="S40" s="8"/>
-      <c r="T40" s="8" t="n">
+      <c r="T40" s="8"/>
+      <c r="U40" s="8"/>
+      <c r="V40" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="U40" s="8"/>
-      <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
       <c r="Y40" s="8"/>
@@ -7441,14 +7441,14 @@
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
+      <c r="S42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T42" s="8"/>
       <c r="U42" s="8"/>
       <c r="V42" s="8"/>
       <c r="W42" s="8"/>
-      <c r="X42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X42" s="8"/>
       <c r="Y42" s="8"/>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
@@ -7491,7 +7491,9 @@
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
+      <c r="S43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
       <c r="V43" s="9"/>
@@ -7500,9 +7502,7 @@
       <c r="Y43" s="9"/>
       <c r="Z43" s="9"/>
       <c r="AA43" s="9"/>
-      <c r="AB43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
       <c r="AD43" s="9"/>
       <c r="AE43" s="9"/>
@@ -7541,13 +7541,13 @@
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
       <c r="R44" s="8"/>
-      <c r="S44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S44" s="8"/>
       <c r="T44" s="8"/>
       <c r="U44" s="8"/>
       <c r="V44" s="8"/>
-      <c r="W44" s="8"/>
+      <c r="W44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="X44" s="8"/>
       <c r="Y44" s="8"/>
       <c r="Z44" s="8"/>
@@ -7599,16 +7599,16 @@
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
       <c r="Z45" s="9"/>
-      <c r="AA45" s="9"/>
+      <c r="AA45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AB45" s="9"/>
       <c r="AC45" s="9"/>
       <c r="AD45" s="9"/>
       <c r="AE45" s="9"/>
       <c r="AF45" s="9"/>
       <c r="AG45" s="9"/>
-      <c r="AH45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH45" s="9"/>
       <c r="AI45" s="9"/>
       <c r="AJ45" s="9"/>
       <c r="AK45" s="9"/>
@@ -7642,14 +7642,14 @@
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
       <c r="S46" s="8"/>
-      <c r="T46" s="8"/>
+      <c r="T46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U46" s="8"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
       <c r="X46" s="8"/>
-      <c r="Y46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Y46" s="8"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
@@ -7791,10 +7791,10 @@
       <c r="P49" s="9"/>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
-      <c r="S49" s="9"/>
-      <c r="T49" s="9" t="n">
+      <c r="S49" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="T49" s="9"/>
       <c r="U49" s="9"/>
       <c r="V49" s="9"/>
       <c r="W49" s="9"/>
@@ -7892,10 +7892,10 @@
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
-      <c r="T51" s="9" t="n">
+      <c r="T51" s="9"/>
+      <c r="U51" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
       <c r="X51" s="9"/>
@@ -7944,7 +7944,9 @@
       <c r="S52" s="8"/>
       <c r="T52" s="8"/>
       <c r="U52" s="8"/>
-      <c r="V52" s="8"/>
+      <c r="V52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="W52" s="8"/>
       <c r="X52" s="8"/>
       <c r="Y52" s="8"/>
@@ -7954,9 +7956,7 @@
       <c r="AC52" s="8"/>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
-      <c r="AF52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AF52" s="8"/>
       <c r="AG52" s="8"/>
       <c r="AH52" s="8"/>
       <c r="AI52" s="8"/>
@@ -7999,11 +7999,11 @@
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
-      <c r="AA53" s="9" t="n">
+      <c r="AA53" s="9"/>
+      <c r="AB53" s="9"/>
+      <c r="AC53" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
       <c r="AD53" s="9"/>
       <c r="AE53" s="9"/>
       <c r="AF53" s="9"/>
@@ -8046,7 +8046,9 @@
       <c r="U54" s="8"/>
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
-      <c r="X54" s="8"/>
+      <c r="X54" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y54" s="8"/>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
@@ -8056,9 +8058,7 @@
       <c r="AE54" s="8"/>
       <c r="AF54" s="8"/>
       <c r="AG54" s="8"/>
-      <c r="AH54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH54" s="8"/>
       <c r="AI54" s="8"/>
       <c r="AJ54" s="8"/>
       <c r="AK54" s="8"/>
@@ -8101,11 +8101,11 @@
       <c r="Z55" s="9"/>
       <c r="AA55" s="9"/>
       <c r="AB55" s="9"/>
-      <c r="AC55" s="9" t="n">
+      <c r="AC55" s="9"/>
+      <c r="AD55" s="9"/>
+      <c r="AE55" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AD55" s="9"/>
-      <c r="AE55" s="9"/>
       <c r="AF55" s="9"/>
       <c r="AG55" s="9"/>
       <c r="AH55" s="9"/>
@@ -8161,11 +8161,11 @@
       <c r="AH56" s="8"/>
       <c r="AI56" s="8"/>
       <c r="AJ56" s="8"/>
-      <c r="AK56" s="8"/>
+      <c r="AK56" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="AL56" s="8"/>
-      <c r="AM56" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="AM56" s="8"/>
       <c r="AN56" s="8"/>
       <c r="AO56" s="8"/>
       <c r="AP56" s="8"/>
@@ -8259,10 +8259,10 @@
       <c r="AH58" s="8"/>
       <c r="AI58" s="8"/>
       <c r="AJ58" s="8"/>
-      <c r="AK58" s="8" t="n">
+      <c r="AK58" s="8"/>
+      <c r="AL58" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="AL58" s="8"/>
       <c r="AM58" s="8"/>
       <c r="AN58" s="8"/>
       <c r="AO58" s="8"/>
@@ -8308,10 +8308,10 @@
       <c r="AH59" s="9"/>
       <c r="AI59" s="9"/>
       <c r="AJ59" s="9"/>
-      <c r="AK59" s="9" t="n">
+      <c r="AK59" s="9"/>
+      <c r="AL59" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AL59" s="9"/>
       <c r="AM59" s="9"/>
       <c r="AN59" s="9"/>
       <c r="AO59" s="9"/>
@@ -8357,11 +8357,11 @@
       <c r="AH60" s="8"/>
       <c r="AI60" s="8"/>
       <c r="AJ60" s="8"/>
-      <c r="AK60" s="8" t="n">
+      <c r="AK60" s="8"/>
+      <c r="AL60" s="8"/>
+      <c r="AM60" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="AL60" s="8"/>
-      <c r="AM60" s="8"/>
       <c r="AN60" s="8"/>
       <c r="AO60" s="8"/>
       <c r="AP60" s="8"/>
@@ -8406,10 +8406,10 @@
       <c r="AH61" s="9"/>
       <c r="AI61" s="9"/>
       <c r="AJ61" s="9"/>
-      <c r="AK61" s="9" t="n">
+      <c r="AK61" s="9"/>
+      <c r="AL61" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="AL61" s="9"/>
       <c r="AM61" s="9"/>
       <c r="AN61" s="9"/>
       <c r="AO61" s="9"/>
@@ -8455,11 +8455,11 @@
       <c r="AH62" s="8"/>
       <c r="AI62" s="8"/>
       <c r="AJ62" s="8"/>
-      <c r="AK62" s="8"/>
+      <c r="AK62" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="AL62" s="8"/>
-      <c r="AM62" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="AM62" s="8"/>
       <c r="AN62" s="8"/>
       <c r="AO62" s="8"/>
       <c r="AP62" s="8"/>
@@ -8557,11 +8557,11 @@
       <c r="AL64" s="8"/>
       <c r="AM64" s="8"/>
       <c r="AN64" s="8"/>
-      <c r="AO64" s="8"/>
+      <c r="AO64" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP64" s="8"/>
-      <c r="AQ64" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ64" s="8"/>
     </row>
     <row r="65" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
       <c r="A65" s="18"/>
@@ -8606,11 +8606,11 @@
       <c r="AL65" s="9"/>
       <c r="AM65" s="9"/>
       <c r="AN65" s="9"/>
-      <c r="AO65" s="9"/>
+      <c r="AO65" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP65" s="9"/>
-      <c r="AQ65" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ65" s="9"/>
     </row>
     <row r="66" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A66" s="18"/>
@@ -8654,11 +8654,11 @@
       <c r="AK66" s="8"/>
       <c r="AL66" s="8"/>
       <c r="AM66" s="8"/>
-      <c r="AN66" s="8"/>
+      <c r="AN66" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AO66" s="8"/>
-      <c r="AP66" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AP66" s="8"/>
       <c r="AQ66" s="8"/>
     </row>
     <row r="67" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -8704,11 +8704,11 @@
       <c r="AL67" s="9"/>
       <c r="AM67" s="9"/>
       <c r="AN67" s="9"/>
-      <c r="AO67" s="9"/>
+      <c r="AO67" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP67" s="9"/>
-      <c r="AQ67" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ67" s="9"/>
     </row>
     <row r="68" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A68" s="18"/>
@@ -8753,10 +8753,10 @@
       <c r="AL68" s="8"/>
       <c r="AM68" s="8"/>
       <c r="AN68" s="8"/>
-      <c r="AO68" s="8" t="n">
+      <c r="AO68" s="8"/>
+      <c r="AP68" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP68" s="8"/>
       <c r="AQ68" s="8"/>
     </row>
     <row r="69" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -8802,10 +8802,10 @@
       <c r="AL69" s="9"/>
       <c r="AM69" s="9"/>
       <c r="AN69" s="9"/>
-      <c r="AO69" s="9"/>
-      <c r="AP69" s="9" t="n">
+      <c r="AO69" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP69" s="9"/>
       <c r="AQ69" s="9"/>
     </row>
     <row r="70" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -8900,11 +8900,11 @@
       <c r="AL71" s="9"/>
       <c r="AM71" s="9"/>
       <c r="AN71" s="9"/>
-      <c r="AO71" s="9"/>
+      <c r="AO71" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP71" s="9"/>
-      <c r="AQ71" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ71" s="9"/>
     </row>
     <row r="72" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A72" s="18"/>
@@ -8949,11 +8949,11 @@
       <c r="AL72" s="8"/>
       <c r="AM72" s="8"/>
       <c r="AN72" s="8"/>
-      <c r="AO72" s="8"/>
+      <c r="AO72" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP72" s="8"/>
-      <c r="AQ72" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ72" s="8"/>
     </row>
     <row r="73" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
       <c r="A73" s="18"/>
@@ -8998,10 +8998,10 @@
       <c r="AL73" s="9"/>
       <c r="AM73" s="9"/>
       <c r="AN73" s="9"/>
-      <c r="AO73" s="9"/>
-      <c r="AP73" s="9" t="n">
+      <c r="AO73" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP73" s="9"/>
       <c r="AQ73" s="9"/>
     </row>
     <row r="74" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -9046,10 +9046,10 @@
       <c r="AK74" s="8"/>
       <c r="AL74" s="8"/>
       <c r="AM74" s="8"/>
-      <c r="AN74" s="8"/>
-      <c r="AO74" s="8" t="n">
+      <c r="AN74" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO74" s="8"/>
       <c r="AP74" s="8"/>
       <c r="AQ74" s="8"/>
     </row>
@@ -9095,10 +9095,10 @@
       <c r="AK75" s="9"/>
       <c r="AL75" s="9"/>
       <c r="AM75" s="9"/>
-      <c r="AN75" s="9" t="n">
+      <c r="AN75" s="9"/>
+      <c r="AO75" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO75" s="9"/>
       <c r="AP75" s="9"/>
       <c r="AQ75" s="9"/>
     </row>
@@ -9145,10 +9145,10 @@
       <c r="AL76" s="8"/>
       <c r="AM76" s="8"/>
       <c r="AN76" s="8"/>
-      <c r="AO76" s="8" t="n">
+      <c r="AO76" s="8"/>
+      <c r="AP76" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP76" s="8"/>
       <c r="AQ76" s="8"/>
     </row>
     <row r="77" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -9194,11 +9194,11 @@
       <c r="AL77" s="9"/>
       <c r="AM77" s="9"/>
       <c r="AN77" s="9"/>
-      <c r="AO77" s="9"/>
+      <c r="AO77" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP77" s="9"/>
-      <c r="AQ77" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ77" s="9"/>
     </row>
     <row r="78" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A78" s="18"/>
@@ -9242,10 +9242,10 @@
       <c r="AK78" s="8"/>
       <c r="AL78" s="8"/>
       <c r="AM78" s="8"/>
-      <c r="AN78" s="8" t="n">
+      <c r="AN78" s="8"/>
+      <c r="AO78" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO78" s="8"/>
       <c r="AP78" s="8"/>
       <c r="AQ78" s="8"/>
     </row>
@@ -9292,11 +9292,11 @@
       <c r="AL79" s="9"/>
       <c r="AM79" s="9"/>
       <c r="AN79" s="9"/>
-      <c r="AO79" s="9"/>
+      <c r="AO79" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP79" s="9"/>
-      <c r="AQ79" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ79" s="9"/>
     </row>
     <row r="80" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A80" s="18"/>
@@ -9326,11 +9326,11 @@
       <c r="W80" s="8"/>
       <c r="X80" s="8"/>
       <c r="Y80" s="8"/>
-      <c r="Z80" s="8" t="n">
+      <c r="Z80" s="8"/>
+      <c r="AA80" s="8"/>
+      <c r="AB80" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AA80" s="8"/>
-      <c r="AB80" s="8"/>
       <c r="AC80" s="8"/>
       <c r="AD80" s="8"/>
       <c r="AE80" s="8"/>
@@ -9369,11 +9369,11 @@
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
       <c r="S81" s="9"/>
-      <c r="T81" s="9" t="n">
+      <c r="T81" s="9"/>
+      <c r="U81" s="9"/>
+      <c r="V81" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="U81" s="9"/>
-      <c r="V81" s="9"/>
       <c r="W81" s="9"/>
       <c r="X81" s="9"/>
       <c r="Y81" s="9"/>
@@ -9426,11 +9426,11 @@
       <c r="Y82" s="8"/>
       <c r="Z82" s="8"/>
       <c r="AA82" s="8"/>
-      <c r="AB82" s="8" t="n">
+      <c r="AB82" s="8"/>
+      <c r="AC82" s="8"/>
+      <c r="AD82" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AC82" s="8"/>
-      <c r="AD82" s="8"/>
       <c r="AE82" s="8"/>
       <c r="AF82" s="8"/>
       <c r="AG82" s="8"/>
@@ -9469,11 +9469,11 @@
       <c r="S83" s="9"/>
       <c r="T83" s="9"/>
       <c r="U83" s="9"/>
-      <c r="V83" s="9" t="n">
+      <c r="V83" s="9"/>
+      <c r="W83" s="9"/>
+      <c r="X83" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="W83" s="9"/>
-      <c r="X83" s="9"/>
       <c r="Y83" s="9"/>
       <c r="Z83" s="9"/>
       <c r="AA83" s="9"/>
@@ -9765,7 +9765,9 @@
         <v>0</v>
       </c>
       <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="D2" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
@@ -9774,9 +9776,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="8" t="n">
-        <v>80</v>
-      </c>
+      <c r="M2" s="8"/>
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -9815,16 +9815,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
+      <c r="D3" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
@@ -9868,15 +9868,15 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+      <c r="M4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
@@ -9916,13 +9916,13 @@
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
-      <c r="E5" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
+      <c r="I5" s="9" t="n">
+        <v>72</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
@@ -9964,13 +9964,13 @@
       <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="n">
-        <v>68</v>
-      </c>
+      <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="G6" s="8" t="n">
+        <v>68</v>
+      </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -10014,11 +10014,11 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
@@ -10064,7 +10064,9 @@
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="8"/>
+      <c r="C8" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -10073,9 +10075,7 @@
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
-      <c r="L8" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
@@ -10114,16 +10114,16 @@
       <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="9"/>
+      <c r="C9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
@@ -10167,15 +10167,15 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
-      <c r="F10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="L10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
@@ -10215,13 +10215,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="9" t="n">
-        <v>28</v>
-      </c>
+      <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="H11" s="9" t="n">
+        <v>28</v>
+      </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
@@ -10267,7 +10267,9 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="F12" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -10276,9 +10278,7 @@
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
-      <c r="O12" s="8" t="n">
-        <v>25</v>
-      </c>
+      <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
@@ -10315,7 +10315,9 @@
         <v>11</v>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
+      <c r="D13" s="9" t="n">
+        <v>86</v>
+      </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
@@ -10324,9 +10326,7 @@
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
-      <c r="M13" s="9" t="n">
-        <v>86</v>
-      </c>
+      <c r="M13" s="9"/>
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
@@ -10365,16 +10365,16 @@
         <v>12</v>
       </c>
       <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
+      <c r="D14" s="8" t="n">
+        <v>55</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
-      <c r="K14" s="8" t="n">
-        <v>55</v>
-      </c>
+      <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -10418,15 +10418,15 @@
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
+      <c r="M15" s="9" t="n">
+        <v>44</v>
+      </c>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
@@ -10466,13 +10466,13 @@
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="8" t="n">
-        <v>50</v>
-      </c>
+      <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
+      <c r="I16" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -10514,13 +10514,13 @@
       <c r="B17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="G17" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
@@ -10564,11 +10564,11 @@
       <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -10614,7 +10614,9 @@
       <c r="B19" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -10623,9 +10625,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
@@ -10669,15 +10669,15 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
+      <c r="N20" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
@@ -10717,13 +10717,13 @@
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="J21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
@@ -10765,13 +10765,13 @@
         <v>20</v>
       </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="H22" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
@@ -10815,11 +10815,11 @@
         <v>21</v>
       </c>
       <c r="C23" s="9"/>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -10865,7 +10865,9 @@
         <v>25</v>
       </c>
       <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
+      <c r="D24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
@@ -10874,9 +10876,7 @@
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
-      <c r="M24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -10915,14 +10915,14 @@
         <v>26</v>
       </c>
       <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
+      <c r="D25" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
@@ -10968,13 +10968,13 @@
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="8" t="n">
-        <v>27</v>
-      </c>
+      <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
+      <c r="K26" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
@@ -11016,13 +11016,13 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
+      <c r="I27" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
@@ -11080,13 +11080,13 @@
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
-      <c r="S28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="S28" s="8"/>
       <c r="T28" s="8"/>
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
+      <c r="W28" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="X28" s="8"/>
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
@@ -11136,13 +11136,13 @@
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
       <c r="X29" s="9"/>
-      <c r="Y29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="Y29" s="9"/>
       <c r="Z29" s="9"/>
       <c r="AA29" s="9"/>
       <c r="AB29" s="9"/>
-      <c r="AC29" s="9"/>
+      <c r="AC29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="AD29" s="9"/>
       <c r="AE29" s="9"/>
       <c r="AF29" s="9"/>
@@ -11183,16 +11183,16 @@
       <c r="S30" s="8"/>
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
-      <c r="V30" s="8"/>
+      <c r="V30" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="W30" s="8"/>
       <c r="X30" s="8"/>
       <c r="Y30" s="8"/>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
-      <c r="AC30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="AC30" s="8"/>
       <c r="AD30" s="8"/>
       <c r="AE30" s="8"/>
       <c r="AF30" s="8"/>
@@ -11233,13 +11233,13 @@
       <c r="S31" s="9"/>
       <c r="T31" s="9"/>
       <c r="U31" s="9"/>
-      <c r="V31" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="V31" s="9"/>
       <c r="W31" s="9"/>
       <c r="X31" s="9"/>
       <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
+      <c r="Z31" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="AA31" s="9"/>
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
@@ -11332,13 +11332,13 @@
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
       <c r="T33" s="9"/>
-      <c r="U33" s="9" t="n">
-        <v>12</v>
-      </c>
+      <c r="U33" s="9"/>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
       <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
+      <c r="Y33" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="Z33" s="9"/>
       <c r="AA33" s="9"/>
       <c r="AB33" s="9"/>
@@ -11381,14 +11381,14 @@
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
       <c r="S34" s="8"/>
-      <c r="T34" s="8"/>
+      <c r="T34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="U34" s="8"/>
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
-      <c r="Y34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="Y34" s="8"/>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
@@ -11431,11 +11431,11 @@
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="9"/>
-      <c r="T35" s="9" t="n">
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
       <c r="Y35" s="9"/>
@@ -11481,9 +11481,7 @@
       <c r="Q36" s="8"/>
       <c r="R36" s="8"/>
       <c r="S36" s="8"/>
-      <c r="T36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T36" s="8"/>
       <c r="U36" s="8"/>
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
@@ -11491,7 +11489,9 @@
       <c r="Y36" s="8"/>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="AB36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AC36" s="8"/>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
@@ -11530,7 +11530,9 @@
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
+      <c r="S37" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
       <c r="V37" s="9"/>
@@ -11539,9 +11541,7 @@
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
       <c r="AA37" s="9"/>
-      <c r="AB37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
       <c r="AD37" s="9"/>
       <c r="AE37" s="9"/>
@@ -11591,13 +11591,13 @@
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
       <c r="AC38" s="8"/>
-      <c r="AD38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
       <c r="AF38" s="8"/>
       <c r="AG38" s="8"/>
-      <c r="AH38" s="8"/>
+      <c r="AH38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AI38" s="8"/>
       <c r="AJ38" s="8"/>
       <c r="AK38" s="8"/>
@@ -11632,13 +11632,13 @@
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
-      <c r="U39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U39" s="9"/>
       <c r="V39" s="9"/>
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
+      <c r="Y39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Z39" s="9"/>
       <c r="AA39" s="9"/>
       <c r="AB39" s="9"/>
@@ -11681,14 +11681,14 @@
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
       <c r="S40" s="8"/>
-      <c r="T40" s="8"/>
+      <c r="T40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U40" s="8"/>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
-      <c r="Y40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Y40" s="8"/>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
       <c r="AB40" s="8"/>
@@ -11731,16 +11731,16 @@
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
+      <c r="T41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U41" s="9"/>
       <c r="V41" s="9"/>
       <c r="W41" s="9"/>
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
-      <c r="AA41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AA41" s="9"/>
       <c r="AB41" s="9"/>
       <c r="AC41" s="9"/>
       <c r="AD41" s="9"/>
@@ -11781,11 +11781,11 @@
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
       <c r="S42" s="8"/>
-      <c r="T42" s="8" t="n">
+      <c r="T42" s="8"/>
+      <c r="U42" s="8"/>
+      <c r="V42" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="U42" s="8"/>
-      <c r="V42" s="8"/>
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
       <c r="Y42" s="8"/>
@@ -11830,10 +11830,10 @@
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
-      <c r="T43" s="9" t="n">
+      <c r="S43" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="T43" s="9"/>
       <c r="U43" s="9"/>
       <c r="V43" s="9"/>
       <c r="W43" s="9"/>
@@ -11880,16 +11880,16 @@
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
       <c r="R44" s="8"/>
-      <c r="S44" s="8"/>
+      <c r="S44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T44" s="8"/>
       <c r="U44" s="8"/>
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
       <c r="Y44" s="8"/>
-      <c r="Z44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
       <c r="AC44" s="8"/>
@@ -11930,11 +11930,11 @@
       <c r="P45" s="9"/>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
-      <c r="S45" s="9" t="n">
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="T45" s="9"/>
-      <c r="U45" s="9"/>
       <c r="V45" s="9"/>
       <c r="W45" s="9"/>
       <c r="X45" s="9"/>
@@ -11982,11 +11982,11 @@
       <c r="R46" s="8"/>
       <c r="S46" s="8"/>
       <c r="T46" s="8"/>
-      <c r="U46" s="8" t="n">
+      <c r="U46" s="8"/>
+      <c r="V46" s="8"/>
+      <c r="W46" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="V46" s="8"/>
-      <c r="W46" s="8"/>
       <c r="X46" s="8"/>
       <c r="Y46" s="8"/>
       <c r="Z46" s="8"/>
@@ -12034,13 +12034,13 @@
       <c r="T47" s="9"/>
       <c r="U47" s="9"/>
       <c r="V47" s="9"/>
-      <c r="W47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="W47" s="9"/>
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
       <c r="Z47" s="9"/>
-      <c r="AA47" s="9"/>
+      <c r="AA47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AB47" s="9"/>
       <c r="AC47" s="9"/>
       <c r="AD47" s="9"/>
@@ -12088,13 +12088,13 @@
       <c r="X48" s="8"/>
       <c r="Y48" s="8"/>
       <c r="Z48" s="8"/>
-      <c r="AA48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AA48" s="8"/>
       <c r="AB48" s="8"/>
       <c r="AC48" s="8"/>
       <c r="AD48" s="8"/>
-      <c r="AE48" s="8"/>
+      <c r="AE48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF48" s="8"/>
       <c r="AG48" s="8"/>
       <c r="AH48" s="8"/>
@@ -12140,13 +12140,13 @@
       <c r="Z49" s="9"/>
       <c r="AA49" s="9"/>
       <c r="AB49" s="9"/>
-      <c r="AC49" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AC49" s="9"/>
       <c r="AD49" s="9"/>
       <c r="AE49" s="9"/>
       <c r="AF49" s="9"/>
-      <c r="AG49" s="9"/>
+      <c r="AG49" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AH49" s="9"/>
       <c r="AI49" s="9"/>
       <c r="AJ49" s="9"/>
@@ -12181,13 +12181,13 @@
       <c r="Q50" s="8"/>
       <c r="R50" s="8"/>
       <c r="S50" s="8"/>
-      <c r="T50" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T50" s="8"/>
       <c r="U50" s="8"/>
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
-      <c r="X50" s="8"/>
+      <c r="X50" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y50" s="8"/>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
@@ -12230,14 +12230,14 @@
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
-      <c r="S51" s="9"/>
+      <c r="S51" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T51" s="9"/>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
-      <c r="X51" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
       <c r="AA51" s="9"/>
@@ -12290,11 +12290,11 @@
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
       <c r="AB52" s="8"/>
-      <c r="AC52" s="8" t="n">
+      <c r="AC52" s="8"/>
+      <c r="AD52" s="8"/>
+      <c r="AE52" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AD52" s="8"/>
-      <c r="AE52" s="8"/>
       <c r="AF52" s="8"/>
       <c r="AG52" s="8"/>
       <c r="AH52" s="8"/>
@@ -12335,11 +12335,11 @@
       <c r="U53" s="9"/>
       <c r="V53" s="9"/>
       <c r="W53" s="9"/>
-      <c r="X53" s="9" t="n">
+      <c r="X53" s="9"/>
+      <c r="Y53" s="9"/>
+      <c r="Z53" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
       <c r="AA53" s="9"/>
       <c r="AB53" s="9"/>
       <c r="AC53" s="9"/>
@@ -12382,7 +12382,9 @@
       <c r="R54" s="8"/>
       <c r="S54" s="8"/>
       <c r="T54" s="8"/>
-      <c r="U54" s="8"/>
+      <c r="U54" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
@@ -12392,9 +12394,7 @@
       <c r="AB54" s="8"/>
       <c r="AC54" s="8"/>
       <c r="AD54" s="8"/>
-      <c r="AE54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE54" s="8"/>
       <c r="AF54" s="8"/>
       <c r="AG54" s="8"/>
       <c r="AH54" s="8"/>
@@ -12437,11 +12437,11 @@
       <c r="W55" s="9"/>
       <c r="X55" s="9"/>
       <c r="Y55" s="9"/>
-      <c r="Z55" s="9" t="n">
+      <c r="Z55" s="9"/>
+      <c r="AA55" s="9"/>
+      <c r="AB55" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
       <c r="AC55" s="9"/>
       <c r="AD55" s="9"/>
       <c r="AE55" s="9"/>
@@ -12549,10 +12549,10 @@
       <c r="AH57" s="9"/>
       <c r="AI57" s="9"/>
       <c r="AJ57" s="9"/>
-      <c r="AK57" s="9"/>
-      <c r="AL57" s="9" t="n">
+      <c r="AK57" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="AL57" s="9"/>
       <c r="AM57" s="9"/>
       <c r="AN57" s="9"/>
       <c r="AO57" s="9"/>
@@ -12794,10 +12794,10 @@
       <c r="AH62" s="8"/>
       <c r="AI62" s="8"/>
       <c r="AJ62" s="8"/>
-      <c r="AK62" s="8" t="n">
+      <c r="AK62" s="8"/>
+      <c r="AL62" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="AL62" s="8"/>
       <c r="AM62" s="8"/>
       <c r="AN62" s="8"/>
       <c r="AO62" s="8"/>
@@ -12843,10 +12843,10 @@
       <c r="AH63" s="9"/>
       <c r="AI63" s="9"/>
       <c r="AJ63" s="9"/>
-      <c r="AK63" s="9"/>
-      <c r="AL63" s="9" t="n">
+      <c r="AK63" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="AL63" s="9"/>
       <c r="AM63" s="9"/>
       <c r="AN63" s="9"/>
       <c r="AO63" s="9"/>
@@ -12896,10 +12896,10 @@
       <c r="AL64" s="8"/>
       <c r="AM64" s="8"/>
       <c r="AN64" s="8"/>
-      <c r="AO64" s="8" t="n">
+      <c r="AO64" s="8"/>
+      <c r="AP64" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP64" s="8"/>
       <c r="AQ64" s="8"/>
     </row>
     <row r="65" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -12993,10 +12993,10 @@
       <c r="AK66" s="8"/>
       <c r="AL66" s="8"/>
       <c r="AM66" s="8"/>
-      <c r="AN66" s="8" t="n">
+      <c r="AN66" s="8"/>
+      <c r="AO66" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO66" s="8"/>
       <c r="AP66" s="8"/>
       <c r="AQ66" s="8"/>
     </row>
@@ -13092,10 +13092,10 @@
       <c r="AL68" s="8"/>
       <c r="AM68" s="8"/>
       <c r="AN68" s="8"/>
-      <c r="AO68" s="8" t="n">
+      <c r="AO68" s="8"/>
+      <c r="AP68" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP68" s="8"/>
       <c r="AQ68" s="8"/>
     </row>
     <row r="69" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -13140,12 +13140,12 @@
       <c r="AK69" s="9"/>
       <c r="AL69" s="9"/>
       <c r="AM69" s="9"/>
-      <c r="AN69" s="9"/>
+      <c r="AN69" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AO69" s="9"/>
       <c r="AP69" s="9"/>
-      <c r="AQ69" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ69" s="9"/>
     </row>
     <row r="70" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A70" s="18"/>
@@ -13189,11 +13189,11 @@
       <c r="AK70" s="8"/>
       <c r="AL70" s="8"/>
       <c r="AM70" s="8"/>
-      <c r="AN70" s="8" t="n">
+      <c r="AN70" s="8"/>
+      <c r="AO70" s="8"/>
+      <c r="AP70" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO70" s="8"/>
-      <c r="AP70" s="8"/>
       <c r="AQ70" s="8"/>
     </row>
     <row r="71" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -13239,10 +13239,10 @@
       <c r="AL71" s="9"/>
       <c r="AM71" s="9"/>
       <c r="AN71" s="9"/>
-      <c r="AO71" s="9"/>
-      <c r="AP71" s="9" t="n">
+      <c r="AO71" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP71" s="9"/>
       <c r="AQ71" s="9"/>
     </row>
     <row r="72" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -13288,10 +13288,10 @@
       <c r="AL72" s="8"/>
       <c r="AM72" s="8"/>
       <c r="AN72" s="8"/>
-      <c r="AO72" s="8"/>
-      <c r="AP72" s="8" t="n">
+      <c r="AO72" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP72" s="8"/>
       <c r="AQ72" s="8"/>
     </row>
     <row r="73" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -13337,11 +13337,11 @@
       <c r="AL73" s="9"/>
       <c r="AM73" s="9"/>
       <c r="AN73" s="9"/>
-      <c r="AO73" s="9"/>
+      <c r="AO73" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP73" s="9"/>
-      <c r="AQ73" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ73" s="9"/>
     </row>
     <row r="74" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A74" s="18"/>
@@ -13434,11 +13434,11 @@
       <c r="AK75" s="9"/>
       <c r="AL75" s="9"/>
       <c r="AM75" s="9"/>
-      <c r="AN75" s="9"/>
+      <c r="AN75" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AO75" s="9"/>
-      <c r="AP75" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AP75" s="9"/>
       <c r="AQ75" s="9"/>
     </row>
     <row r="76" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -13483,10 +13483,10 @@
       <c r="AK76" s="8"/>
       <c r="AL76" s="8"/>
       <c r="AM76" s="8"/>
-      <c r="AN76" s="8"/>
-      <c r="AO76" s="8" t="n">
+      <c r="AN76" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO76" s="8"/>
       <c r="AP76" s="8"/>
       <c r="AQ76" s="8"/>
     </row>
@@ -13581,10 +13581,10 @@
       <c r="AK78" s="8"/>
       <c r="AL78" s="8"/>
       <c r="AM78" s="8"/>
-      <c r="AN78" s="8" t="n">
+      <c r="AN78" s="8"/>
+      <c r="AO78" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO78" s="8"/>
       <c r="AP78" s="8"/>
       <c r="AQ78" s="8"/>
     </row>
@@ -13630,10 +13630,10 @@
       <c r="AK79" s="9"/>
       <c r="AL79" s="9"/>
       <c r="AM79" s="9"/>
-      <c r="AN79" s="9"/>
-      <c r="AO79" s="9" t="n">
+      <c r="AN79" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO79" s="9"/>
       <c r="AP79" s="9"/>
       <c r="AQ79" s="9"/>
     </row>
@@ -13661,12 +13661,12 @@
       <c r="S80" s="8"/>
       <c r="T80" s="8"/>
       <c r="U80" s="8"/>
-      <c r="V80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="V80" s="8"/>
       <c r="W80" s="8"/>
       <c r="X80" s="8"/>
-      <c r="Y80" s="8"/>
+      <c r="Y80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Z80" s="8"/>
       <c r="AA80" s="8"/>
       <c r="AB80" s="8"/>
@@ -13707,7 +13707,9 @@
       <c r="P81" s="9"/>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
-      <c r="S81" s="9"/>
+      <c r="S81" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T81" s="9"/>
       <c r="U81" s="9"/>
       <c r="V81" s="9"/>
@@ -13718,9 +13720,7 @@
       <c r="AA81" s="9"/>
       <c r="AB81" s="9"/>
       <c r="AC81" s="9"/>
-      <c r="AD81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD81" s="9"/>
       <c r="AE81" s="9"/>
       <c r="AF81" s="9"/>
       <c r="AG81" s="9"/>
@@ -13761,12 +13761,12 @@
       <c r="U82" s="8"/>
       <c r="V82" s="8"/>
       <c r="W82" s="8"/>
-      <c r="X82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X82" s="8"/>
       <c r="Y82" s="8"/>
       <c r="Z82" s="8"/>
-      <c r="AA82" s="8"/>
+      <c r="AA82" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AB82" s="8"/>
       <c r="AC82" s="8"/>
       <c r="AD82" s="8"/>
@@ -13805,11 +13805,11 @@
       <c r="P83" s="9"/>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
-      <c r="S83" s="9" t="n">
+      <c r="S83" s="9"/>
+      <c r="T83" s="9"/>
+      <c r="U83" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="T83" s="9"/>
-      <c r="U83" s="9"/>
       <c r="V83" s="9"/>
       <c r="W83" s="9"/>
       <c r="X83" s="9"/>
@@ -14107,13 +14107,13 @@
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
-      <c r="G2" s="8" t="n">
-        <v>80</v>
-      </c>
+      <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="K2" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
@@ -14155,13 +14155,13 @@
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
-      <c r="E3" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
+      <c r="I3" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
@@ -14203,13 +14203,13 @@
       <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="G4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -14253,7 +14253,9 @@
       <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="9" t="n">
+        <v>72</v>
+      </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
@@ -14262,9 +14264,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
-      <c r="L5" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="L5" s="9"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -14303,16 +14303,16 @@
       <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="8"/>
+      <c r="C6" s="8" t="n">
+        <v>68</v>
+      </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="8" t="n">
-        <v>68</v>
-      </c>
+      <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
@@ -14358,13 +14358,13 @@
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
+      <c r="L7" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
@@ -14406,13 +14406,13 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
+      <c r="J8" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
@@ -14454,13 +14454,13 @@
         <v>7</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="H9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -14504,7 +14504,9 @@
         <v>8</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="D10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -14513,9 +14515,7 @@
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
-      <c r="M10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -14554,16 +14554,16 @@
         <v>9</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
+      <c r="D11" s="9" t="n">
+        <v>28</v>
+      </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="9" t="n">
-        <v>28</v>
-      </c>
+      <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
@@ -14609,13 +14609,13 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="8" t="n">
-        <v>25</v>
-      </c>
+      <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
+      <c r="M12" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -14657,13 +14657,13 @@
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
-      <c r="G13" s="9" t="n">
-        <v>86</v>
-      </c>
+      <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
+      <c r="K13" s="9" t="n">
+        <v>86</v>
+      </c>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
@@ -14703,15 +14703,15 @@
       <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8" t="n">
-        <v>55</v>
-      </c>
+      <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="I14" s="8" t="n">
+        <v>55</v>
+      </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -14753,11 +14753,11 @@
       <c r="B15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
@@ -14803,7 +14803,9 @@
       <c r="B16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="8"/>
+      <c r="C16" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -14812,9 +14814,7 @@
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
-      <c r="L16" s="8" t="n">
-        <v>50</v>
-      </c>
+      <c r="L16" s="8"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
@@ -14853,16 +14853,16 @@
       <c r="B17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="9"/>
+      <c r="C17" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
@@ -14908,13 +14908,13 @@
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="H18" s="8"/>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
+      <c r="L18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
@@ -14954,15 +14954,15 @@
         <v>17</v>
       </c>
       <c r="C19" s="9"/>
-      <c r="D19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="J19" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
@@ -15004,11 +15004,11 @@
         <v>18</v>
       </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
@@ -15054,7 +15054,9 @@
         <v>19</v>
       </c>
       <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
+      <c r="D21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
@@ -15063,9 +15065,7 @@
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
-      <c r="M21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="M21" s="9"/>
       <c r="N21" s="9"/>
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
@@ -15104,16 +15104,16 @@
         <v>20</v>
       </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="D22" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
-      <c r="K22" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
@@ -15159,13 +15159,13 @@
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
+      <c r="M23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="N23" s="9"/>
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
@@ -15207,13 +15207,13 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
-      <c r="G24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
+      <c r="K24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
@@ -15253,15 +15253,15 @@
       <c r="B25" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="I25" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
@@ -15303,11 +15303,11 @@
       <c r="B26" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
@@ -15353,7 +15353,9 @@
       <c r="B27" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -15362,9 +15364,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
       <c r="O27" s="9"/>
@@ -15420,15 +15420,15 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
+      <c r="T28" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
       <c r="X28" s="8"/>
       <c r="Y28" s="8"/>
-      <c r="Z28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
       <c r="AC28" s="8"/>
@@ -15469,10 +15469,10 @@
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
-      <c r="S29" s="9" t="n">
+      <c r="S29" s="9"/>
+      <c r="T29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="9"/>
       <c r="U29" s="9"/>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -15523,13 +15523,13 @@
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
-      <c r="W30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="W30" s="8"/>
       <c r="X30" s="8"/>
       <c r="Y30" s="8"/>
       <c r="Z30" s="8"/>
-      <c r="AA30" s="8"/>
+      <c r="AA30" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="AB30" s="8"/>
       <c r="AC30" s="8"/>
       <c r="AD30" s="8"/>
@@ -15622,13 +15622,13 @@
       <c r="S32" s="8"/>
       <c r="T32" s="8"/>
       <c r="U32" s="8"/>
-      <c r="V32" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="V32" s="8"/>
       <c r="W32" s="8"/>
       <c r="X32" s="8"/>
       <c r="Y32" s="8"/>
-      <c r="Z32" s="8"/>
+      <c r="Z32" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="AA32" s="8"/>
       <c r="AB32" s="8"/>
       <c r="AC32" s="8"/>
@@ -15669,16 +15669,16 @@
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
+      <c r="S33" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
       <c r="X33" s="9"/>
       <c r="Y33" s="9"/>
-      <c r="Z33" s="9" t="n">
-        <v>12</v>
-      </c>
+      <c r="Z33" s="9"/>
       <c r="AA33" s="9"/>
       <c r="AB33" s="9"/>
       <c r="AC33" s="9"/>
@@ -15719,13 +15719,13 @@
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
-      <c r="S34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="S34" s="8"/>
       <c r="T34" s="8"/>
       <c r="U34" s="8"/>
       <c r="V34" s="8"/>
-      <c r="W34" s="8"/>
+      <c r="W34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="X34" s="8"/>
       <c r="Y34" s="8"/>
       <c r="Z34" s="8"/>
@@ -15770,14 +15770,14 @@
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
+      <c r="T35" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="U35" s="9"/>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
-      <c r="Y35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="Y35" s="9"/>
       <c r="Z35" s="9"/>
       <c r="AA35" s="9"/>
       <c r="AB35" s="9"/>
@@ -15822,7 +15822,9 @@
       <c r="S36" s="8"/>
       <c r="T36" s="8"/>
       <c r="U36" s="8"/>
-      <c r="V36" s="8"/>
+      <c r="V36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
       <c r="Y36" s="8"/>
@@ -15831,9 +15833,7 @@
       <c r="AB36" s="8"/>
       <c r="AC36" s="8"/>
       <c r="AD36" s="8"/>
-      <c r="AE36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE36" s="8"/>
       <c r="AF36" s="8"/>
       <c r="AG36" s="8"/>
       <c r="AH36" s="8"/>
@@ -15870,15 +15870,15 @@
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
-      <c r="T37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T37" s="9"/>
       <c r="U37" s="9"/>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
-      <c r="Z37" s="9"/>
+      <c r="Z37" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AA37" s="9"/>
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
@@ -15919,14 +15919,14 @@
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
       <c r="R38" s="8"/>
-      <c r="S38" s="8"/>
+      <c r="S38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T38" s="8"/>
       <c r="U38" s="8"/>
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
-      <c r="X38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X38" s="8"/>
       <c r="Y38" s="8"/>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
@@ -16019,13 +16019,13 @@
       <c r="P40" s="8"/>
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
-      <c r="S40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S40" s="8"/>
       <c r="T40" s="8"/>
       <c r="U40" s="8"/>
       <c r="V40" s="8"/>
-      <c r="W40" s="8"/>
+      <c r="W40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="X40" s="8"/>
       <c r="Y40" s="8"/>
       <c r="Z40" s="8"/>
@@ -16071,15 +16071,15 @@
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
       <c r="T41" s="9"/>
-      <c r="U41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U41" s="9"/>
       <c r="V41" s="9"/>
       <c r="W41" s="9"/>
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
-      <c r="AA41" s="9"/>
+      <c r="AA41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AB41" s="9"/>
       <c r="AC41" s="9"/>
       <c r="AD41" s="9"/>
@@ -16120,14 +16120,14 @@
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
       <c r="S42" s="8"/>
-      <c r="T42" s="8"/>
+      <c r="T42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U42" s="8"/>
       <c r="V42" s="8"/>
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
-      <c r="Y42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Y42" s="8"/>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
       <c r="AB42" s="8"/>
@@ -16170,7 +16170,9 @@
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
-      <c r="T43" s="9"/>
+      <c r="T43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U43" s="9"/>
       <c r="V43" s="9"/>
       <c r="W43" s="9"/>
@@ -16179,9 +16181,7 @@
       <c r="Z43" s="9"/>
       <c r="AA43" s="9"/>
       <c r="AB43" s="9"/>
-      <c r="AC43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AC43" s="9"/>
       <c r="AD43" s="9"/>
       <c r="AE43" s="9"/>
       <c r="AF43" s="9"/>
@@ -16220,13 +16220,13 @@
       <c r="Q44" s="8"/>
       <c r="R44" s="8"/>
       <c r="S44" s="8"/>
-      <c r="T44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T44" s="8"/>
       <c r="U44" s="8"/>
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
-      <c r="X44" s="8"/>
+      <c r="X44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y44" s="8"/>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
@@ -16272,13 +16272,13 @@
       <c r="S45" s="9"/>
       <c r="T45" s="9"/>
       <c r="U45" s="9"/>
-      <c r="V45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="V45" s="9"/>
       <c r="W45" s="9"/>
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
-      <c r="Z45" s="9"/>
+      <c r="Z45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AA45" s="9"/>
       <c r="AB45" s="9"/>
       <c r="AC45" s="9"/>
@@ -16319,16 +16319,16 @@
       <c r="P46" s="8"/>
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
+      <c r="S46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
       <c r="X46" s="8"/>
       <c r="Y46" s="8"/>
-      <c r="Z46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
       <c r="AC46" s="8"/>
@@ -16369,11 +16369,11 @@
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
-      <c r="S47" s="9" t="n">
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="T47" s="9"/>
-      <c r="U47" s="9"/>
       <c r="V47" s="9"/>
       <c r="W47" s="9"/>
       <c r="X47" s="9"/>
@@ -16419,9 +16419,7 @@
       <c r="P48" s="8"/>
       <c r="Q48" s="8"/>
       <c r="R48" s="8"/>
-      <c r="S48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S48" s="8"/>
       <c r="T48" s="8"/>
       <c r="U48" s="8"/>
       <c r="V48" s="8"/>
@@ -16438,7 +16436,9 @@
       <c r="AG48" s="8"/>
       <c r="AH48" s="8"/>
       <c r="AI48" s="8"/>
-      <c r="AJ48" s="8"/>
+      <c r="AJ48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AK48" s="8"/>
       <c r="AL48" s="8"/>
       <c r="AM48" s="8"/>
@@ -16473,13 +16473,13 @@
       <c r="T49" s="9"/>
       <c r="U49" s="9"/>
       <c r="V49" s="9"/>
-      <c r="W49" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="W49" s="9"/>
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
       <c r="Z49" s="9"/>
-      <c r="AA49" s="9"/>
+      <c r="AA49" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AB49" s="9"/>
       <c r="AC49" s="9"/>
       <c r="AD49" s="9"/>
@@ -16520,16 +16520,16 @@
       <c r="Q50" s="8"/>
       <c r="R50" s="8"/>
       <c r="S50" s="8"/>
-      <c r="T50" s="8"/>
+      <c r="T50" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U50" s="8"/>
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
       <c r="Y50" s="8"/>
       <c r="Z50" s="8"/>
-      <c r="AA50" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
       <c r="AC50" s="8"/>
       <c r="AD50" s="8"/>
@@ -16570,11 +16570,11 @@
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
-      <c r="T51" s="9" t="n">
+      <c r="T51" s="9"/>
+      <c r="U51" s="9"/>
+      <c r="V51" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
       <c r="W51" s="9"/>
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
@@ -16626,11 +16626,11 @@
       <c r="W52" s="8"/>
       <c r="X52" s="8"/>
       <c r="Y52" s="8"/>
-      <c r="Z52" s="8" t="n">
+      <c r="Z52" s="8"/>
+      <c r="AA52" s="8"/>
+      <c r="AB52" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AA52" s="8"/>
-      <c r="AB52" s="8"/>
       <c r="AC52" s="8"/>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
@@ -16671,11 +16671,11 @@
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
       <c r="T53" s="9"/>
-      <c r="U53" s="9" t="n">
+      <c r="U53" s="9"/>
+      <c r="V53" s="9"/>
+      <c r="W53" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
@@ -16728,11 +16728,11 @@
       <c r="Y54" s="8"/>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
-      <c r="AB54" s="8" t="n">
+      <c r="AB54" s="8"/>
+      <c r="AC54" s="8"/>
+      <c r="AD54" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AC54" s="8"/>
-      <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
       <c r="AF54" s="8"/>
       <c r="AG54" s="8"/>
@@ -16773,11 +16773,11 @@
       <c r="T55" s="9"/>
       <c r="U55" s="9"/>
       <c r="V55" s="9"/>
-      <c r="W55" s="9" t="n">
+      <c r="W55" s="9"/>
+      <c r="X55" s="9"/>
+      <c r="Y55" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
       <c r="AA55" s="9"/>
       <c r="AB55" s="9"/>
@@ -16839,10 +16839,10 @@
       <c r="AH56" s="8"/>
       <c r="AI56" s="8"/>
       <c r="AJ56" s="8"/>
-      <c r="AK56" s="8"/>
-      <c r="AL56" s="8" t="n">
+      <c r="AK56" s="8" t="n">
         <v>15</v>
       </c>
+      <c r="AL56" s="8"/>
       <c r="AM56" s="8"/>
       <c r="AN56" s="8"/>
       <c r="AO56" s="8"/>
@@ -16889,10 +16889,10 @@
       <c r="AI57" s="9"/>
       <c r="AJ57" s="9"/>
       <c r="AK57" s="9"/>
-      <c r="AL57" s="9" t="n">
+      <c r="AL57" s="9"/>
+      <c r="AM57" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AM57" s="9"/>
       <c r="AN57" s="9"/>
       <c r="AO57" s="9"/>
       <c r="AP57" s="9"/>
@@ -16937,10 +16937,10 @@
       <c r="AH58" s="8"/>
       <c r="AI58" s="8"/>
       <c r="AJ58" s="8"/>
-      <c r="AK58" s="8" t="n">
+      <c r="AK58" s="8"/>
+      <c r="AL58" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="AL58" s="8"/>
       <c r="AM58" s="8"/>
       <c r="AN58" s="8"/>
       <c r="AO58" s="8"/>
@@ -16987,10 +16987,10 @@
       <c r="AI59" s="9"/>
       <c r="AJ59" s="9"/>
       <c r="AK59" s="9"/>
-      <c r="AL59" s="9"/>
-      <c r="AM59" s="9" t="n">
+      <c r="AL59" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="AM59" s="9"/>
       <c r="AN59" s="9"/>
       <c r="AO59" s="9"/>
       <c r="AP59" s="9"/>
@@ -17035,11 +17035,11 @@
       <c r="AH60" s="8"/>
       <c r="AI60" s="8"/>
       <c r="AJ60" s="8"/>
-      <c r="AK60" s="8" t="n">
+      <c r="AK60" s="8"/>
+      <c r="AL60" s="8"/>
+      <c r="AM60" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="AL60" s="8"/>
-      <c r="AM60" s="8"/>
       <c r="AN60" s="8"/>
       <c r="AO60" s="8"/>
       <c r="AP60" s="8"/>
@@ -17332,11 +17332,11 @@
       <c r="AK66" s="8"/>
       <c r="AL66" s="8"/>
       <c r="AM66" s="8"/>
-      <c r="AN66" s="8" t="n">
+      <c r="AN66" s="8"/>
+      <c r="AO66" s="8"/>
+      <c r="AP66" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO66" s="8"/>
-      <c r="AP66" s="8"/>
       <c r="AQ66" s="8"/>
     </row>
     <row r="67" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -17382,10 +17382,10 @@
       <c r="AL67" s="9"/>
       <c r="AM67" s="9"/>
       <c r="AN67" s="9"/>
-      <c r="AO67" s="9" t="n">
+      <c r="AO67" s="9"/>
+      <c r="AP67" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP67" s="9"/>
       <c r="AQ67" s="9"/>
     </row>
     <row r="68" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -17627,10 +17627,10 @@
       <c r="AL72" s="8"/>
       <c r="AM72" s="8"/>
       <c r="AN72" s="8"/>
-      <c r="AO72" s="8" t="n">
+      <c r="AO72" s="8"/>
+      <c r="AP72" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP72" s="8"/>
       <c r="AQ72" s="8"/>
     </row>
     <row r="73" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -17725,10 +17725,10 @@
       <c r="AL74" s="8"/>
       <c r="AM74" s="8"/>
       <c r="AN74" s="8"/>
-      <c r="AO74" s="8"/>
-      <c r="AP74" s="8" t="n">
+      <c r="AO74" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP74" s="8"/>
       <c r="AQ74" s="8"/>
     </row>
     <row r="75" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -17822,11 +17822,11 @@
       <c r="AK76" s="8"/>
       <c r="AL76" s="8"/>
       <c r="AM76" s="8"/>
-      <c r="AN76" s="8"/>
+      <c r="AN76" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AO76" s="8"/>
-      <c r="AP76" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AP76" s="8"/>
       <c r="AQ76" s="8"/>
     </row>
     <row r="77" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -17920,10 +17920,10 @@
       <c r="AK78" s="8"/>
       <c r="AL78" s="8"/>
       <c r="AM78" s="8"/>
-      <c r="AN78" s="8" t="n">
+      <c r="AN78" s="8"/>
+      <c r="AO78" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO78" s="8"/>
       <c r="AP78" s="8"/>
       <c r="AQ78" s="8"/>
     </row>
@@ -17969,11 +17969,11 @@
       <c r="AK79" s="9"/>
       <c r="AL79" s="9"/>
       <c r="AM79" s="9"/>
-      <c r="AN79" s="9"/>
+      <c r="AN79" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AO79" s="9"/>
-      <c r="AP79" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AP79" s="9"/>
       <c r="AQ79" s="9"/>
     </row>
     <row r="80" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -17997,11 +17997,11 @@
       <c r="P80" s="8"/>
       <c r="Q80" s="8"/>
       <c r="R80" s="8"/>
-      <c r="S80" s="8" t="n">
+      <c r="S80" s="8"/>
+      <c r="T80" s="8"/>
+      <c r="U80" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="T80" s="8"/>
-      <c r="U80" s="8"/>
       <c r="V80" s="8"/>
       <c r="W80" s="8"/>
       <c r="X80" s="8"/>
@@ -18054,11 +18054,11 @@
       <c r="X81" s="9"/>
       <c r="Y81" s="9"/>
       <c r="Z81" s="9"/>
-      <c r="AA81" s="9" t="n">
+      <c r="AA81" s="9"/>
+      <c r="AB81" s="9"/>
+      <c r="AC81" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB81" s="9"/>
-      <c r="AC81" s="9"/>
       <c r="AD81" s="9"/>
       <c r="AE81" s="9"/>
       <c r="AF81" s="9"/>
@@ -18097,9 +18097,7 @@
       <c r="R82" s="8"/>
       <c r="S82" s="8"/>
       <c r="T82" s="8"/>
-      <c r="U82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U82" s="8"/>
       <c r="V82" s="8"/>
       <c r="W82" s="8"/>
       <c r="X82" s="8"/>
@@ -18114,7 +18112,9 @@
       <c r="AG82" s="8"/>
       <c r="AH82" s="8"/>
       <c r="AI82" s="8"/>
-      <c r="AJ82" s="8"/>
+      <c r="AJ82" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AK82" s="8"/>
       <c r="AL82" s="8"/>
       <c r="AM82" s="8"/>
@@ -18154,11 +18154,11 @@
       <c r="Z83" s="9"/>
       <c r="AA83" s="9"/>
       <c r="AB83" s="9"/>
-      <c r="AC83" s="9" t="n">
+      <c r="AC83" s="9"/>
+      <c r="AD83" s="9"/>
+      <c r="AE83" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AD83" s="9"/>
-      <c r="AE83" s="9"/>
       <c r="AF83" s="9"/>
       <c r="AG83" s="9"/>
       <c r="AH83" s="9"/>
@@ -18444,16 +18444,16 @@
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
+      <c r="E2" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
-      <c r="L2" s="8" t="n">
-        <v>80</v>
-      </c>
+      <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
@@ -18492,16 +18492,16 @@
       <c r="B3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="9"/>
+      <c r="C3" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="J3" s="9"/>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
@@ -18547,13 +18547,13 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
-      <c r="H4" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="L4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
@@ -18595,13 +18595,13 @@
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
+      <c r="J5" s="9" t="n">
+        <v>72</v>
+      </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
@@ -18643,13 +18643,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="8"/>
-      <c r="D6" s="8" t="n">
-        <v>68</v>
-      </c>
+      <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="H6" s="8" t="n">
+        <v>68</v>
+      </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
@@ -18695,16 +18695,16 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="F7" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
-      <c r="M7" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
@@ -18743,16 +18743,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
+      <c r="D8" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
-      <c r="K8" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="K8" s="8"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
@@ -18798,13 +18798,13 @@
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="I9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
+      <c r="M9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
@@ -18846,13 +18846,13 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
-      <c r="G10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="K10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
@@ -18894,13 +18894,13 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="9" t="n">
-        <v>28</v>
-      </c>
+      <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="I11" s="9" t="n">
+        <v>28</v>
+      </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -18942,13 +18942,13 @@
       <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="8" t="n">
-        <v>25</v>
-      </c>
+      <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="G12" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
@@ -18994,16 +18994,16 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="E13" s="9" t="n">
+        <v>86</v>
+      </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="9" t="n">
-        <v>86</v>
-      </c>
+      <c r="L13" s="9"/>
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
@@ -19042,16 +19042,16 @@
       <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8"/>
+      <c r="C14" s="8" t="n">
+        <v>55</v>
+      </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
-      <c r="J14" s="8" t="n">
-        <v>55</v>
-      </c>
+      <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
@@ -19097,13 +19097,13 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
+      <c r="L15" s="9" t="n">
+        <v>44</v>
+      </c>
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
@@ -19145,13 +19145,13 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="8" t="n">
-        <v>50</v>
-      </c>
+      <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
+      <c r="J16" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
@@ -19193,13 +19193,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="H17" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
@@ -19245,16 +19245,16 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="F18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
-      <c r="M18" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="M18" s="8"/>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -19293,16 +19293,16 @@
         <v>17</v>
       </c>
       <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
+      <c r="D19" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
-      <c r="K19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
@@ -19348,13 +19348,13 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="I20" s="8"/>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
+      <c r="M20" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
@@ -19396,13 +19396,13 @@
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
+      <c r="K21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
@@ -19444,13 +19444,13 @@
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
+      <c r="I22" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
@@ -19492,13 +19492,13 @@
       <c r="B23" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="G23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
@@ -19544,16 +19544,16 @@
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="E24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
-      <c r="L24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
@@ -19592,16 +19592,16 @@
       <c r="B25" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
-      <c r="J25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
@@ -19647,13 +19647,13 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
-      <c r="H26" s="8" t="n">
-        <v>27</v>
-      </c>
+      <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
+      <c r="L26" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
@@ -19695,13 +19695,13 @@
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
+      <c r="J27" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
@@ -19759,13 +19759,13 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="8"/>
-      <c r="T28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="T28" s="8"/>
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
-      <c r="X28" s="8"/>
+      <c r="X28" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
@@ -19808,14 +19808,14 @@
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
+      <c r="S29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="T29" s="9"/>
       <c r="U29" s="9"/>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
-      <c r="X29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="X29" s="9"/>
       <c r="Y29" s="9"/>
       <c r="Z29" s="9"/>
       <c r="AA29" s="9"/>
@@ -19858,11 +19858,11 @@
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
-      <c r="S30" s="8" t="n">
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
       <c r="X30" s="8"/>
@@ -19912,13 +19912,13 @@
       <c r="T31" s="9"/>
       <c r="U31" s="9"/>
       <c r="V31" s="9"/>
-      <c r="W31" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="W31" s="9"/>
       <c r="X31" s="9"/>
       <c r="Y31" s="9"/>
       <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
+      <c r="AA31" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
       <c r="AD31" s="9"/>
@@ -19959,16 +19959,16 @@
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
       <c r="S32" s="8"/>
-      <c r="T32" s="8"/>
+      <c r="T32" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="8"/>
       <c r="X32" s="8"/>
       <c r="Y32" s="8"/>
       <c r="Z32" s="8"/>
-      <c r="AA32" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="AA32" s="8"/>
       <c r="AB32" s="8"/>
       <c r="AC32" s="8"/>
       <c r="AD32" s="8"/>
@@ -20009,13 +20009,13 @@
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
-      <c r="T33" s="9" t="n">
-        <v>12</v>
-      </c>
+      <c r="T33" s="9"/>
       <c r="U33" s="9"/>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
+      <c r="X33" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
       <c r="AA33" s="9"/>
@@ -20058,16 +20058,16 @@
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
+      <c r="S34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="T34" s="8"/>
       <c r="U34" s="8"/>
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
       <c r="Y34" s="8"/>
-      <c r="Z34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
       <c r="AC34" s="8"/>
@@ -20108,13 +20108,13 @@
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
-      <c r="S35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="S35" s="9"/>
       <c r="T35" s="9"/>
       <c r="U35" s="9"/>
       <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
+      <c r="W35" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="X35" s="9"/>
       <c r="Y35" s="9"/>
       <c r="Z35" s="9"/>
@@ -20208,10 +20208,10 @@
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
-      <c r="S37" s="9" t="n">
+      <c r="S37" s="9"/>
+      <c r="T37" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="T37" s="9"/>
       <c r="U37" s="9"/>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -20258,12 +20258,12 @@
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
       <c r="R38" s="8"/>
-      <c r="S38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S38" s="8"/>
       <c r="T38" s="8"/>
       <c r="U38" s="8"/>
-      <c r="V38" s="8"/>
+      <c r="V38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
       <c r="Y38" s="8"/>
@@ -20311,13 +20311,13 @@
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
       <c r="U39" s="9"/>
-      <c r="V39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="V39" s="9"/>
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
+      <c r="Z39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AA39" s="9"/>
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
@@ -20359,13 +20359,13 @@
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
       <c r="S40" s="8"/>
-      <c r="T40" s="8"/>
+      <c r="T40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U40" s="8"/>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
-      <c r="X40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X40" s="8"/>
       <c r="Y40" s="8"/>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
@@ -20408,11 +20408,11 @@
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
+      <c r="S41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T41" s="9"/>
-      <c r="U41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U41" s="9"/>
       <c r="V41" s="9"/>
       <c r="W41" s="9"/>
       <c r="X41" s="9"/>
@@ -20458,13 +20458,13 @@
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
-      <c r="S42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S42" s="8"/>
       <c r="T42" s="8"/>
       <c r="U42" s="8"/>
       <c r="V42" s="8"/>
-      <c r="W42" s="8"/>
+      <c r="W42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="X42" s="8"/>
       <c r="Y42" s="8"/>
       <c r="Z42" s="8"/>
@@ -20508,7 +20508,9 @@
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
+      <c r="S43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
       <c r="V43" s="9"/>
@@ -20523,9 +20525,7 @@
       <c r="AE43" s="9"/>
       <c r="AF43" s="9"/>
       <c r="AG43" s="9"/>
-      <c r="AH43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH43" s="9"/>
       <c r="AI43" s="9"/>
       <c r="AJ43" s="9"/>
       <c r="AK43" s="9"/>
@@ -20559,14 +20559,14 @@
       <c r="Q44" s="8"/>
       <c r="R44" s="8"/>
       <c r="S44" s="8"/>
-      <c r="T44" s="8"/>
+      <c r="T44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U44" s="8"/>
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
-      <c r="Y44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Y44" s="8"/>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
@@ -20659,13 +20659,13 @@
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
       <c r="S46" s="8"/>
-      <c r="T46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T46" s="8"/>
       <c r="U46" s="8"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
-      <c r="X46" s="8"/>
+      <c r="X46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y46" s="8"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
@@ -20708,12 +20708,12 @@
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
-      <c r="S47" s="9"/>
+      <c r="S47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T47" s="9"/>
       <c r="U47" s="9"/>
-      <c r="V47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="V47" s="9"/>
       <c r="W47" s="9"/>
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
@@ -20758,16 +20758,16 @@
       <c r="P48" s="8"/>
       <c r="Q48" s="8"/>
       <c r="R48" s="8"/>
-      <c r="S48" s="8"/>
+      <c r="S48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T48" s="8"/>
       <c r="U48" s="8"/>
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
       <c r="X48" s="8"/>
       <c r="Y48" s="8"/>
-      <c r="Z48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
       <c r="AB48" s="8"/>
       <c r="AC48" s="8"/>
@@ -20808,11 +20808,11 @@
       <c r="P49" s="9"/>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
-      <c r="S49" s="9" t="n">
+      <c r="S49" s="9"/>
+      <c r="T49" s="9"/>
+      <c r="U49" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="T49" s="9"/>
-      <c r="U49" s="9"/>
       <c r="V49" s="9"/>
       <c r="W49" s="9"/>
       <c r="X49" s="9"/>
@@ -20858,15 +20858,15 @@
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
       <c r="R50" s="8"/>
-      <c r="S50" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S50" s="8"/>
       <c r="T50" s="8"/>
       <c r="U50" s="8"/>
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
-      <c r="Y50" s="8"/>
+      <c r="Y50" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
@@ -20912,15 +20912,15 @@
       <c r="T51" s="9"/>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
-      <c r="W51" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="W51" s="9"/>
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
       <c r="AA51" s="9"/>
       <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
+      <c r="AC51" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AD51" s="9"/>
       <c r="AE51" s="9"/>
       <c r="AF51" s="9"/>
@@ -20962,11 +20962,11 @@
       <c r="T52" s="8"/>
       <c r="U52" s="8"/>
       <c r="V52" s="8"/>
-      <c r="W52" s="8" t="n">
+      <c r="W52" s="8"/>
+      <c r="X52" s="8"/>
+      <c r="Y52" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="X52" s="8"/>
-      <c r="Y52" s="8"/>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
       <c r="AB52" s="8"/>
@@ -21009,7 +21009,9 @@
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
-      <c r="T53" s="9"/>
+      <c r="T53" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U53" s="9"/>
       <c r="V53" s="9"/>
       <c r="W53" s="9"/>
@@ -21019,9 +21021,7 @@
       <c r="AA53" s="9"/>
       <c r="AB53" s="9"/>
       <c r="AC53" s="9"/>
-      <c r="AD53" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD53" s="9"/>
       <c r="AE53" s="9"/>
       <c r="AF53" s="9"/>
       <c r="AG53" s="9"/>
@@ -21064,11 +21064,11 @@
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
-      <c r="Y54" s="8" t="n">
+      <c r="Y54" s="8"/>
+      <c r="Z54" s="8"/>
+      <c r="AA54" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="Z54" s="8"/>
-      <c r="AA54" s="8"/>
       <c r="AB54" s="8"/>
       <c r="AC54" s="8"/>
       <c r="AD54" s="8"/>
@@ -21109,11 +21109,11 @@
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
       <c r="S55" s="9"/>
-      <c r="T55" s="9" t="n">
+      <c r="T55" s="9"/>
+      <c r="U55" s="9"/>
+      <c r="V55" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
       <c r="W55" s="9"/>
       <c r="X55" s="9"/>
       <c r="Y55" s="9"/>
@@ -21374,11 +21374,11 @@
       <c r="AH60" s="8"/>
       <c r="AI60" s="8"/>
       <c r="AJ60" s="8"/>
-      <c r="AK60" s="8" t="n">
+      <c r="AK60" s="8"/>
+      <c r="AL60" s="8"/>
+      <c r="AM60" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="AL60" s="8"/>
-      <c r="AM60" s="8"/>
       <c r="AN60" s="8"/>
       <c r="AO60" s="8"/>
       <c r="AP60" s="8"/>
@@ -21575,10 +21575,10 @@
       <c r="AM64" s="8"/>
       <c r="AN64" s="8"/>
       <c r="AO64" s="8"/>
-      <c r="AP64" s="8"/>
-      <c r="AQ64" s="8" t="n">
+      <c r="AP64" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AQ64" s="8"/>
     </row>
     <row r="65" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
       <c r="A65" s="18"/>
@@ -21623,11 +21623,11 @@
       <c r="AL65" s="9"/>
       <c r="AM65" s="9"/>
       <c r="AN65" s="9"/>
-      <c r="AO65" s="9"/>
+      <c r="AO65" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP65" s="9"/>
-      <c r="AQ65" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ65" s="9"/>
     </row>
     <row r="66" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A66" s="18"/>
@@ -21671,12 +21671,12 @@
       <c r="AK66" s="8"/>
       <c r="AL66" s="8"/>
       <c r="AM66" s="8"/>
-      <c r="AN66" s="8"/>
+      <c r="AN66" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AO66" s="8"/>
       <c r="AP66" s="8"/>
-      <c r="AQ66" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ66" s="8"/>
     </row>
     <row r="67" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
       <c r="A67" s="18"/>
@@ -21721,10 +21721,10 @@
       <c r="AL67" s="9"/>
       <c r="AM67" s="9"/>
       <c r="AN67" s="9"/>
-      <c r="AO67" s="9"/>
-      <c r="AP67" s="9" t="n">
+      <c r="AO67" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP67" s="9"/>
       <c r="AQ67" s="9"/>
     </row>
     <row r="68" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -21770,10 +21770,10 @@
       <c r="AL68" s="8"/>
       <c r="AM68" s="8"/>
       <c r="AN68" s="8"/>
-      <c r="AO68" s="8"/>
-      <c r="AP68" s="8" t="n">
+      <c r="AO68" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP68" s="8"/>
       <c r="AQ68" s="8"/>
     </row>
     <row r="69" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -21819,10 +21819,10 @@
       <c r="AL69" s="9"/>
       <c r="AM69" s="9"/>
       <c r="AN69" s="9"/>
-      <c r="AO69" s="9" t="n">
+      <c r="AO69" s="9"/>
+      <c r="AP69" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP69" s="9"/>
       <c r="AQ69" s="9"/>
     </row>
     <row r="70" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -21868,11 +21868,11 @@
       <c r="AL70" s="8"/>
       <c r="AM70" s="8"/>
       <c r="AN70" s="8"/>
-      <c r="AO70" s="8"/>
+      <c r="AO70" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP70" s="8"/>
-      <c r="AQ70" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ70" s="8"/>
     </row>
     <row r="71" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
       <c r="A71" s="18"/>
@@ -22015,11 +22015,11 @@
       <c r="AL73" s="9"/>
       <c r="AM73" s="9"/>
       <c r="AN73" s="9"/>
-      <c r="AO73" s="9"/>
+      <c r="AO73" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP73" s="9"/>
-      <c r="AQ73" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ73" s="9"/>
     </row>
     <row r="74" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A74" s="18"/>
@@ -22064,10 +22064,10 @@
       <c r="AL74" s="8"/>
       <c r="AM74" s="8"/>
       <c r="AN74" s="8"/>
-      <c r="AO74" s="8"/>
-      <c r="AP74" s="8" t="n">
+      <c r="AO74" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP74" s="8"/>
       <c r="AQ74" s="8"/>
     </row>
     <row r="75" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -22112,10 +22112,10 @@
       <c r="AK75" s="9"/>
       <c r="AL75" s="9"/>
       <c r="AM75" s="9"/>
-      <c r="AN75" s="9" t="n">
+      <c r="AN75" s="9"/>
+      <c r="AO75" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO75" s="9"/>
       <c r="AP75" s="9"/>
       <c r="AQ75" s="9"/>
     </row>
@@ -22210,10 +22210,10 @@
       <c r="AK77" s="9"/>
       <c r="AL77" s="9"/>
       <c r="AM77" s="9"/>
-      <c r="AN77" s="9"/>
-      <c r="AO77" s="9" t="n">
+      <c r="AN77" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO77" s="9"/>
       <c r="AP77" s="9"/>
       <c r="AQ77" s="9"/>
     </row>
@@ -22259,10 +22259,10 @@
       <c r="AK78" s="8"/>
       <c r="AL78" s="8"/>
       <c r="AM78" s="8"/>
-      <c r="AN78" s="8" t="n">
+      <c r="AN78" s="8"/>
+      <c r="AO78" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO78" s="8"/>
       <c r="AP78" s="8"/>
       <c r="AQ78" s="8"/>
     </row>
@@ -22309,11 +22309,11 @@
       <c r="AL79" s="9"/>
       <c r="AM79" s="9"/>
       <c r="AN79" s="9"/>
-      <c r="AO79" s="9"/>
+      <c r="AO79" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AP79" s="9"/>
-      <c r="AQ79" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ79" s="9"/>
     </row>
     <row r="80" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
       <c r="A80" s="18"/>
@@ -22346,11 +22346,11 @@
       <c r="Z80" s="8"/>
       <c r="AA80" s="8"/>
       <c r="AB80" s="8"/>
-      <c r="AC80" s="8" t="n">
+      <c r="AC80" s="8"/>
+      <c r="AD80" s="8"/>
+      <c r="AE80" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AD80" s="8"/>
-      <c r="AE80" s="8"/>
       <c r="AF80" s="8"/>
       <c r="AG80" s="8"/>
       <c r="AH80" s="8"/>
@@ -22392,7 +22392,9 @@
       <c r="W81" s="9"/>
       <c r="X81" s="9"/>
       <c r="Y81" s="9"/>
-      <c r="Z81" s="9"/>
+      <c r="Z81" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AA81" s="9"/>
       <c r="AB81" s="9"/>
       <c r="AC81" s="9"/>
@@ -22402,9 +22404,7 @@
       <c r="AG81" s="9"/>
       <c r="AH81" s="9"/>
       <c r="AI81" s="9"/>
-      <c r="AJ81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AJ81" s="9"/>
       <c r="AK81" s="9"/>
       <c r="AL81" s="9"/>
       <c r="AM81" s="9"/>
@@ -22435,7 +22435,9 @@
       <c r="Q82" s="8"/>
       <c r="R82" s="8"/>
       <c r="S82" s="8"/>
-      <c r="T82" s="8"/>
+      <c r="T82" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U82" s="8"/>
       <c r="V82" s="8"/>
       <c r="W82" s="8"/>
@@ -22446,9 +22448,7 @@
       <c r="AB82" s="8"/>
       <c r="AC82" s="8"/>
       <c r="AD82" s="8"/>
-      <c r="AE82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE82" s="8"/>
       <c r="AF82" s="8"/>
       <c r="AG82" s="8"/>
       <c r="AH82" s="8"/>
@@ -22490,11 +22490,11 @@
       <c r="W83" s="9"/>
       <c r="X83" s="9"/>
       <c r="Y83" s="9"/>
-      <c r="Z83" s="9" t="n">
+      <c r="Z83" s="9"/>
+      <c r="AA83" s="9"/>
+      <c r="AB83" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AA83" s="9"/>
-      <c r="AB83" s="9"/>
       <c r="AC83" s="9"/>
       <c r="AD83" s="9"/>
       <c r="AE83" s="9"/>
@@ -22784,13 +22784,13 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
-      <c r="F2" s="8" t="n">
-        <v>80</v>
-      </c>
+      <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="J2" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
@@ -22832,13 +22832,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="9"/>
-      <c r="D3" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
+      <c r="H3" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
@@ -22884,7 +22884,9 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="F4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
@@ -22893,9 +22895,7 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
-      <c r="O4" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
@@ -22932,7 +22932,9 @@
         <v>3</v>
       </c>
       <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
+      <c r="D5" s="9" t="n">
+        <v>72</v>
+      </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
@@ -22941,9 +22943,7 @@
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
-      <c r="M5" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
@@ -22987,15 +22987,15 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="8" t="n">
-        <v>68</v>
-      </c>
+      <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
+      <c r="O6" s="8" t="n">
+        <v>68</v>
+      </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
@@ -23035,13 +23035,13 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
+      <c r="K7" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
@@ -23083,13 +23083,13 @@
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="I8" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -23131,13 +23131,13 @@
       <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="G9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -23183,7 +23183,9 @@
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="E10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
@@ -23192,9 +23194,7 @@
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
-      <c r="N10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
@@ -23231,7 +23231,9 @@
       <c r="B11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="9" t="n">
+        <v>28</v>
+      </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
@@ -23240,9 +23242,7 @@
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
-      <c r="L11" s="9" t="n">
-        <v>28</v>
-      </c>
+      <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
@@ -23286,15 +23286,15 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="8" t="n">
-        <v>25</v>
-      </c>
+      <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
+      <c r="N12" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
@@ -23334,13 +23334,13 @@
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="9" t="n">
-        <v>86</v>
-      </c>
+      <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="J13" s="9" t="n">
+        <v>86</v>
+      </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
@@ -23382,13 +23382,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="8"/>
-      <c r="D14" s="8" t="n">
-        <v>55</v>
-      </c>
+      <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="H14" s="8" t="n">
+        <v>55</v>
+      </c>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
@@ -23434,7 +23434,9 @@
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="F15" s="9" t="n">
+        <v>44</v>
+      </c>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
@@ -23443,9 +23445,7 @@
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="O15" s="9"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -23482,7 +23482,9 @@
         <v>14</v>
       </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="D16" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -23491,9 +23493,7 @@
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
-      <c r="M16" s="8" t="n">
-        <v>50</v>
-      </c>
+      <c r="M16" s="8"/>
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -23537,15 +23537,15 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="O17" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
@@ -23585,13 +23585,13 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
-      <c r="G18" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
+      <c r="K18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
@@ -23633,13 +23633,13 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
+      <c r="I19" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
@@ -23681,13 +23681,13 @@
       <c r="B20" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="G20" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
@@ -23733,7 +23733,9 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="E21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
@@ -23742,9 +23744,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
-      <c r="N21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="N21" s="9"/>
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
@@ -23781,16 +23781,16 @@
       <c r="B22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="8"/>
+      <c r="C22" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
@@ -23836,13 +23836,13 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
+      <c r="L23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
       <c r="O23" s="9"/>
@@ -23884,13 +23884,13 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
+      <c r="J24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
@@ -23932,13 +23932,13 @@
         <v>26</v>
       </c>
       <c r="C25" s="9"/>
-      <c r="D25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
+      <c r="H25" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
@@ -23984,7 +23984,9 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+      <c r="F26" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
@@ -23993,9 +23995,7 @@
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
-      <c r="O26" s="8" t="n">
-        <v>27</v>
-      </c>
+      <c r="O26" s="8"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
@@ -24032,16 +24032,16 @@
         <v>28</v>
       </c>
       <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
+      <c r="D27" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
-      <c r="K27" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
@@ -24098,14 +24098,14 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
+      <c r="T28" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
       <c r="X28" s="8"/>
-      <c r="Y28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
@@ -24148,11 +24148,11 @@
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
-      <c r="T29" s="9" t="n">
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
       <c r="W29" s="9"/>
       <c r="X29" s="9"/>
       <c r="Y29" s="9"/>
@@ -24198,13 +24198,13 @@
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
       <c r="S30" s="8"/>
-      <c r="T30" s="8"/>
+      <c r="T30" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
-      <c r="X30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="X30" s="8"/>
       <c r="Y30" s="8"/>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
@@ -24248,10 +24248,10 @@
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="9"/>
+      <c r="U31" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="U31" s="9"/>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
       <c r="X31" s="9"/>
@@ -24297,10 +24297,10 @@
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
-      <c r="S32" s="8"/>
-      <c r="T32" s="8" t="n">
+      <c r="S32" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="T32" s="8"/>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
       <c r="W32" s="8"/>
@@ -24348,16 +24348,16 @@
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
+      <c r="T33" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="U33" s="9"/>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
       <c r="X33" s="9"/>
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
-      <c r="AA33" s="9" t="n">
-        <v>12</v>
-      </c>
+      <c r="AA33" s="9"/>
       <c r="AB33" s="9"/>
       <c r="AC33" s="9"/>
       <c r="AD33" s="9"/>
@@ -24398,13 +24398,13 @@
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
       <c r="S34" s="8"/>
-      <c r="T34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="T34" s="8"/>
       <c r="U34" s="8"/>
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
-      <c r="X34" s="8"/>
+      <c r="X34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="Y34" s="8"/>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
@@ -24447,16 +24447,16 @@
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
+      <c r="S35" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="T35" s="9"/>
       <c r="U35" s="9"/>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
       <c r="Y35" s="9"/>
-      <c r="Z35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="Z35" s="9"/>
       <c r="AA35" s="9"/>
       <c r="AB35" s="9"/>
       <c r="AC35" s="9"/>
@@ -24508,13 +24508,13 @@
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
       <c r="AF36" s="8"/>
       <c r="AG36" s="8"/>
-      <c r="AH36" s="8"/>
+      <c r="AH36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AI36" s="8"/>
       <c r="AJ36" s="8"/>
       <c r="AK36" s="8"/>
@@ -24549,13 +24549,13 @@
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
-      <c r="U37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U37" s="9"/>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
-      <c r="Y37" s="9"/>
+      <c r="Y37" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Z37" s="9"/>
       <c r="AA37" s="9"/>
       <c r="AB37" s="9"/>
@@ -24598,14 +24598,14 @@
       <c r="Q38" s="8"/>
       <c r="R38" s="8"/>
       <c r="S38" s="8"/>
-      <c r="T38" s="8"/>
+      <c r="T38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U38" s="8"/>
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
-      <c r="Y38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Y38" s="8"/>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
@@ -24648,16 +24648,16 @@
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
+      <c r="T39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U39" s="9"/>
       <c r="V39" s="9"/>
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
-      <c r="AA39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AA39" s="9"/>
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="9"/>
@@ -24698,11 +24698,11 @@
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
       <c r="S40" s="8"/>
-      <c r="T40" s="8" t="n">
+      <c r="T40" s="8"/>
+      <c r="U40" s="8"/>
+      <c r="V40" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="U40" s="8"/>
-      <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
       <c r="Y40" s="8"/>
@@ -24750,13 +24750,13 @@
       <c r="S41" s="9"/>
       <c r="T41" s="9"/>
       <c r="U41" s="9"/>
-      <c r="V41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="V41" s="9"/>
       <c r="W41" s="9"/>
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
-      <c r="Z41" s="9"/>
+      <c r="Z41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AA41" s="9"/>
       <c r="AB41" s="9"/>
       <c r="AC41" s="9"/>
@@ -24797,16 +24797,16 @@
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
+      <c r="S42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T42" s="8"/>
       <c r="U42" s="8"/>
       <c r="V42" s="8"/>
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
       <c r="Y42" s="8"/>
-      <c r="Z42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
@@ -24847,9 +24847,7 @@
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
-      <c r="S43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S43" s="9"/>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
       <c r="V43" s="9"/>
@@ -24862,7 +24860,9 @@
       <c r="AC43" s="9"/>
       <c r="AD43" s="9"/>
       <c r="AE43" s="9"/>
-      <c r="AF43" s="9"/>
+      <c r="AF43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AG43" s="9"/>
       <c r="AH43" s="9"/>
       <c r="AI43" s="9"/>
@@ -24897,13 +24897,13 @@
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
       <c r="R44" s="8"/>
-      <c r="S44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S44" s="8"/>
       <c r="T44" s="8"/>
       <c r="U44" s="8"/>
       <c r="V44" s="8"/>
-      <c r="W44" s="8"/>
+      <c r="W44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="X44" s="8"/>
       <c r="Y44" s="8"/>
       <c r="Z44" s="8"/>
@@ -24951,13 +24951,13 @@
       <c r="T45" s="9"/>
       <c r="U45" s="9"/>
       <c r="V45" s="9"/>
-      <c r="W45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="W45" s="9"/>
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
       <c r="Z45" s="9"/>
-      <c r="AA45" s="9"/>
+      <c r="AA45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AB45" s="9"/>
       <c r="AC45" s="9"/>
       <c r="AD45" s="9"/>
@@ -24998,16 +24998,16 @@
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
       <c r="S46" s="8"/>
-      <c r="T46" s="8"/>
+      <c r="T46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U46" s="8"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
       <c r="X46" s="8"/>
       <c r="Y46" s="8"/>
       <c r="Z46" s="8"/>
-      <c r="AA46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
       <c r="AC46" s="8"/>
       <c r="AD46" s="8"/>
@@ -25048,9 +25048,7 @@
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
       <c r="S47" s="9"/>
-      <c r="T47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T47" s="9"/>
       <c r="U47" s="9"/>
       <c r="V47" s="9"/>
       <c r="W47" s="9"/>
@@ -25063,7 +25061,9 @@
       <c r="AD47" s="9"/>
       <c r="AE47" s="9"/>
       <c r="AF47" s="9"/>
-      <c r="AG47" s="9"/>
+      <c r="AG47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AH47" s="9"/>
       <c r="AI47" s="9"/>
       <c r="AJ47" s="9"/>
@@ -25097,14 +25097,14 @@
       <c r="P48" s="8"/>
       <c r="Q48" s="8"/>
       <c r="R48" s="8"/>
-      <c r="S48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S48" s="8"/>
       <c r="T48" s="8"/>
       <c r="U48" s="8"/>
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
-      <c r="X48" s="8"/>
+      <c r="X48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y48" s="8"/>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
@@ -25152,13 +25152,13 @@
       <c r="U49" s="9"/>
       <c r="V49" s="9"/>
       <c r="W49" s="9"/>
-      <c r="X49" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
       <c r="Z49" s="9"/>
       <c r="AA49" s="9"/>
-      <c r="AB49" s="9"/>
+      <c r="AB49" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AC49" s="9"/>
       <c r="AD49" s="9"/>
       <c r="AE49" s="9"/>
@@ -25197,16 +25197,16 @@
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
       <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
+      <c r="S50" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T50" s="8"/>
       <c r="U50" s="8"/>
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
       <c r="Y50" s="8"/>
-      <c r="Z50" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
       <c r="AC50" s="8"/>
@@ -25247,11 +25247,11 @@
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
-      <c r="S51" s="9" t="n">
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
       <c r="X51" s="9"/>
@@ -25298,11 +25298,11 @@
       <c r="Q52" s="8"/>
       <c r="R52" s="8"/>
       <c r="S52" s="8"/>
-      <c r="T52" s="8" t="n">
+      <c r="T52" s="8"/>
+      <c r="U52" s="8"/>
+      <c r="V52" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="U52" s="8"/>
-      <c r="V52" s="8"/>
       <c r="W52" s="8"/>
       <c r="X52" s="8"/>
       <c r="Y52" s="8"/>
@@ -25355,11 +25355,11 @@
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
-      <c r="AA53" s="9" t="n">
+      <c r="AA53" s="9"/>
+      <c r="AB53" s="9"/>
+      <c r="AC53" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
       <c r="AD53" s="9"/>
       <c r="AE53" s="9"/>
       <c r="AF53" s="9"/>
@@ -25400,11 +25400,11 @@
       <c r="S54" s="8"/>
       <c r="T54" s="8"/>
       <c r="U54" s="8"/>
-      <c r="V54" s="8" t="n">
+      <c r="V54" s="8"/>
+      <c r="W54" s="8"/>
+      <c r="X54" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="W54" s="8"/>
-      <c r="X54" s="8"/>
       <c r="Y54" s="8"/>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
@@ -25447,7 +25447,9 @@
       <c r="P55" s="9"/>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
-      <c r="S55" s="9"/>
+      <c r="S55" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T55" s="9"/>
       <c r="U55" s="9"/>
       <c r="V55" s="9"/>
@@ -25457,9 +25459,7 @@
       <c r="Z55" s="9"/>
       <c r="AA55" s="9"/>
       <c r="AB55" s="9"/>
-      <c r="AC55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AC55" s="9"/>
       <c r="AD55" s="9"/>
       <c r="AE55" s="9"/>
       <c r="AF55" s="9"/>
@@ -25616,10 +25616,10 @@
       <c r="AI58" s="8"/>
       <c r="AJ58" s="8"/>
       <c r="AK58" s="8"/>
-      <c r="AL58" s="8"/>
-      <c r="AM58" s="8" t="n">
+      <c r="AL58" s="8" t="n">
         <v>14</v>
       </c>
+      <c r="AM58" s="8"/>
       <c r="AN58" s="8"/>
       <c r="AO58" s="8"/>
       <c r="AP58" s="8"/>
@@ -25714,10 +25714,10 @@
       <c r="AI60" s="8"/>
       <c r="AJ60" s="8"/>
       <c r="AK60" s="8"/>
-      <c r="AL60" s="8" t="n">
+      <c r="AL60" s="8"/>
+      <c r="AM60" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="AM60" s="8"/>
       <c r="AN60" s="8"/>
       <c r="AO60" s="8"/>
       <c r="AP60" s="8"/>
@@ -25912,11 +25912,11 @@
       <c r="AK64" s="8"/>
       <c r="AL64" s="8"/>
       <c r="AM64" s="8"/>
-      <c r="AN64" s="8" t="n">
+      <c r="AN64" s="8"/>
+      <c r="AO64" s="8"/>
+      <c r="AP64" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO64" s="8"/>
-      <c r="AP64" s="8"/>
       <c r="AQ64" s="8"/>
     </row>
     <row r="65" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -25961,10 +25961,10 @@
       <c r="AK65" s="9"/>
       <c r="AL65" s="9"/>
       <c r="AM65" s="9"/>
-      <c r="AN65" s="9"/>
-      <c r="AO65" s="9" t="n">
+      <c r="AN65" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO65" s="9"/>
       <c r="AP65" s="9"/>
       <c r="AQ65" s="9"/>
     </row>
@@ -26011,10 +26011,10 @@
       <c r="AL66" s="8"/>
       <c r="AM66" s="8"/>
       <c r="AN66" s="8"/>
-      <c r="AO66" s="8"/>
-      <c r="AP66" s="8" t="n">
+      <c r="AO66" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP66" s="8"/>
       <c r="AQ66" s="8"/>
     </row>
     <row r="67" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -26256,10 +26256,10 @@
       <c r="AL71" s="9"/>
       <c r="AM71" s="9"/>
       <c r="AN71" s="9"/>
-      <c r="AO71" s="9"/>
-      <c r="AP71" s="9" t="n">
+      <c r="AO71" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP71" s="9"/>
       <c r="AQ71" s="9"/>
     </row>
     <row r="72" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -26304,11 +26304,11 @@
       <c r="AK72" s="8"/>
       <c r="AL72" s="8"/>
       <c r="AM72" s="8"/>
-      <c r="AN72" s="8" t="n">
+      <c r="AN72" s="8"/>
+      <c r="AO72" s="8"/>
+      <c r="AP72" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO72" s="8"/>
-      <c r="AP72" s="8"/>
       <c r="AQ72" s="8"/>
     </row>
     <row r="73" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -26354,10 +26354,10 @@
       <c r="AL73" s="9"/>
       <c r="AM73" s="9"/>
       <c r="AN73" s="9"/>
-      <c r="AO73" s="9"/>
-      <c r="AP73" s="9" t="n">
+      <c r="AO73" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP73" s="9"/>
       <c r="AQ73" s="9"/>
     </row>
     <row r="74" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -26451,10 +26451,10 @@
       <c r="AK75" s="9"/>
       <c r="AL75" s="9"/>
       <c r="AM75" s="9"/>
-      <c r="AN75" s="9" t="n">
+      <c r="AN75" s="9"/>
+      <c r="AO75" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO75" s="9"/>
       <c r="AP75" s="9"/>
       <c r="AQ75" s="9"/>
     </row>
@@ -26500,10 +26500,10 @@
       <c r="AK76" s="8"/>
       <c r="AL76" s="8"/>
       <c r="AM76" s="8"/>
-      <c r="AN76" s="8"/>
-      <c r="AO76" s="8" t="n">
+      <c r="AN76" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO76" s="8"/>
       <c r="AP76" s="8"/>
       <c r="AQ76" s="8"/>
     </row>
@@ -26549,10 +26549,10 @@
       <c r="AK77" s="9"/>
       <c r="AL77" s="9"/>
       <c r="AM77" s="9"/>
-      <c r="AN77" s="9"/>
-      <c r="AO77" s="9" t="n">
+      <c r="AN77" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO77" s="9"/>
       <c r="AP77" s="9"/>
       <c r="AQ77" s="9"/>
     </row>
@@ -26599,10 +26599,10 @@
       <c r="AL78" s="8"/>
       <c r="AM78" s="8"/>
       <c r="AN78" s="8"/>
-      <c r="AO78" s="8" t="n">
+      <c r="AO78" s="8"/>
+      <c r="AP78" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP78" s="8"/>
       <c r="AQ78" s="8"/>
     </row>
     <row r="79" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -26682,11 +26682,11 @@
       <c r="W80" s="8"/>
       <c r="X80" s="8"/>
       <c r="Y80" s="8"/>
-      <c r="Z80" s="8" t="n">
+      <c r="Z80" s="8"/>
+      <c r="AA80" s="8"/>
+      <c r="AB80" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AA80" s="8"/>
-      <c r="AB80" s="8"/>
       <c r="AC80" s="8"/>
       <c r="AD80" s="8"/>
       <c r="AE80" s="8"/>
@@ -26725,9 +26725,7 @@
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
       <c r="S81" s="9"/>
-      <c r="T81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T81" s="9"/>
       <c r="U81" s="9"/>
       <c r="V81" s="9"/>
       <c r="W81" s="9"/>
@@ -26742,7 +26740,9 @@
       <c r="AF81" s="9"/>
       <c r="AG81" s="9"/>
       <c r="AH81" s="9"/>
-      <c r="AI81" s="9"/>
+      <c r="AI81" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AJ81" s="9"/>
       <c r="AK81" s="9"/>
       <c r="AL81" s="9"/>
@@ -26782,11 +26782,11 @@
       <c r="Y82" s="8"/>
       <c r="Z82" s="8"/>
       <c r="AA82" s="8"/>
-      <c r="AB82" s="8" t="n">
+      <c r="AB82" s="8"/>
+      <c r="AC82" s="8"/>
+      <c r="AD82" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AC82" s="8"/>
-      <c r="AD82" s="8"/>
       <c r="AE82" s="8"/>
       <c r="AF82" s="8"/>
       <c r="AG82" s="8"/>
@@ -26825,12 +26825,12 @@
       <c r="S83" s="9"/>
       <c r="T83" s="9"/>
       <c r="U83" s="9"/>
-      <c r="V83" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="V83" s="9"/>
       <c r="W83" s="9"/>
       <c r="X83" s="9"/>
-      <c r="Y83" s="9"/>
+      <c r="Y83" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Z83" s="9"/>
       <c r="AA83" s="9"/>
       <c r="AB83" s="9"/>
@@ -27121,7 +27121,9 @@
         <v>0</v>
       </c>
       <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="D2" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
@@ -27130,9 +27132,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="8" t="n">
-        <v>80</v>
-      </c>
+      <c r="M2" s="8"/>
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -27178,13 +27178,13 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
+      <c r="O3" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
@@ -27221,9 +27221,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="8"/>
-      <c r="D4" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
@@ -27232,7 +27230,9 @@
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+      <c r="M4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
@@ -27274,13 +27274,13 @@
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
+      <c r="K5" s="9" t="n">
+        <v>72</v>
+      </c>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
@@ -27320,10 +27320,10 @@
       <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -27372,7 +27372,9 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="E7" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
@@ -27381,9 +27383,7 @@
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
@@ -27420,7 +27420,9 @@
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="8"/>
+      <c r="C8" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -27429,9 +27431,7 @@
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
-      <c r="L8" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
@@ -27477,13 +27477,13 @@
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
+      <c r="N9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
@@ -27525,13 +27525,13 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="L10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
@@ -27571,15 +27571,15 @@
         <v>9</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="9" t="n">
-        <v>28</v>
-      </c>
+      <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="J11" s="9" t="n">
+        <v>28</v>
+      </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
@@ -27623,7 +27623,9 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="F12" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -27632,9 +27634,7 @@
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
-      <c r="O12" s="8" t="n">
-        <v>25</v>
-      </c>
+      <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
@@ -27671,13 +27671,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
+      <c r="D13" s="9" t="n">
+        <v>86</v>
+      </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="9" t="n">
-        <v>86</v>
-      </c>
+      <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
@@ -27728,13 +27728,13 @@
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
-      <c r="K14" s="8" t="n">
-        <v>55</v>
-      </c>
+      <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
+      <c r="O14" s="8" t="n">
+        <v>55</v>
+      </c>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
@@ -27771,9 +27771,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="9"/>
-      <c r="D15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
@@ -27782,7 +27780,9 @@
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
+      <c r="M15" s="9" t="n">
+        <v>44</v>
+      </c>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
@@ -27822,15 +27822,15 @@
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="8" t="n">
-        <v>50</v>
-      </c>
+      <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+      <c r="K16" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
@@ -27870,13 +27870,13 @@
       <c r="B17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="G17" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
@@ -27922,7 +27922,9 @@
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="E18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -27931,9 +27933,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
-      <c r="N18" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
@@ -27970,7 +27970,9 @@
       <c r="B19" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -27979,9 +27981,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
@@ -28027,13 +28027,13 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
+      <c r="N20" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
@@ -28073,15 +28073,15 @@
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
+      <c r="L21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
       <c r="O21" s="9"/>
@@ -28121,13 +28121,13 @@
         <v>20</v>
       </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="H22" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
@@ -28173,7 +28173,9 @@
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
+      <c r="F23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -28182,9 +28184,7 @@
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="O23" s="9"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
@@ -28221,7 +28221,9 @@
         <v>25</v>
       </c>
       <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
+      <c r="D24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
@@ -28230,9 +28232,7 @@
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
-      <c r="M24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
@@ -28278,13 +28278,13 @@
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
-      <c r="K25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="K25" s="9"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="O25" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -28321,9 +28321,7 @@
         <v>27</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="8" t="n">
-        <v>27</v>
-      </c>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -28332,7 +28330,9 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
+      <c r="M26" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -28372,15 +28372,15 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
+      <c r="K27" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
@@ -28436,13 +28436,13 @@
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
-      <c r="S28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="S28" s="8"/>
       <c r="T28" s="8"/>
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
+      <c r="W28" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="X28" s="8"/>
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
@@ -28492,13 +28492,13 @@
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
       <c r="X29" s="9"/>
-      <c r="Y29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="Y29" s="9"/>
       <c r="Z29" s="9"/>
       <c r="AA29" s="9"/>
       <c r="AB29" s="9"/>
-      <c r="AC29" s="9"/>
+      <c r="AC29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="AD29" s="9"/>
       <c r="AE29" s="9"/>
       <c r="AF29" s="9"/>
@@ -28539,7 +28539,9 @@
       <c r="S30" s="8"/>
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
-      <c r="V30" s="8"/>
+      <c r="V30" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="W30" s="8"/>
       <c r="X30" s="8"/>
       <c r="Y30" s="8"/>
@@ -28548,9 +28550,7 @@
       <c r="AB30" s="8"/>
       <c r="AC30" s="8"/>
       <c r="AD30" s="8"/>
-      <c r="AE30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="AE30" s="8"/>
       <c r="AF30" s="8"/>
       <c r="AG30" s="8"/>
       <c r="AH30" s="8"/>
@@ -28589,15 +28589,15 @@
       <c r="S31" s="9"/>
       <c r="T31" s="9"/>
       <c r="U31" s="9"/>
-      <c r="V31" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="V31" s="9"/>
       <c r="W31" s="9"/>
       <c r="X31" s="9"/>
       <c r="Y31" s="9"/>
       <c r="Z31" s="9"/>
       <c r="AA31" s="9"/>
-      <c r="AB31" s="9"/>
+      <c r="AB31" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="AC31" s="9"/>
       <c r="AD31" s="9"/>
       <c r="AE31" s="9"/>
@@ -28636,7 +28636,9 @@
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
-      <c r="S32" s="8"/>
+      <c r="S32" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="T32" s="8"/>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
@@ -28645,9 +28647,7 @@
       <c r="Y32" s="8"/>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8"/>
-      <c r="AB32" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB32" s="8"/>
       <c r="AC32" s="8"/>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
@@ -28688,13 +28688,13 @@
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
       <c r="T33" s="9"/>
-      <c r="U33" s="9" t="n">
-        <v>12</v>
-      </c>
+      <c r="U33" s="9"/>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
       <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
+      <c r="Y33" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="Z33" s="9"/>
       <c r="AA33" s="9"/>
       <c r="AB33" s="9"/>
@@ -28744,13 +28744,13 @@
       <c r="X34" s="8"/>
       <c r="Y34" s="8"/>
       <c r="Z34" s="8"/>
-      <c r="AA34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
       <c r="AC34" s="8"/>
       <c r="AD34" s="8"/>
-      <c r="AE34" s="8"/>
+      <c r="AE34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="AF34" s="8"/>
       <c r="AG34" s="8"/>
       <c r="AH34" s="8"/>
@@ -28798,13 +28798,13 @@
       <c r="AB35" s="9"/>
       <c r="AC35" s="9"/>
       <c r="AD35" s="9"/>
-      <c r="AE35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="AE35" s="9"/>
       <c r="AF35" s="9"/>
       <c r="AG35" s="9"/>
       <c r="AH35" s="9"/>
-      <c r="AI35" s="9"/>
+      <c r="AI35" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="AJ35" s="9"/>
       <c r="AK35" s="9"/>
       <c r="AL35" s="9"/>
@@ -28841,13 +28841,13 @@
       <c r="U36" s="8"/>
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
-      <c r="X36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X36" s="8"/>
       <c r="Y36" s="8"/>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="AB36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AC36" s="8"/>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
@@ -28886,7 +28886,9 @@
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
+      <c r="S37" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
       <c r="V37" s="9"/>
@@ -28895,9 +28897,7 @@
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
       <c r="AA37" s="9"/>
-      <c r="AB37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
       <c r="AD37" s="9"/>
       <c r="AE37" s="9"/>
@@ -28940,16 +28940,16 @@
       <c r="T38" s="8"/>
       <c r="U38" s="8"/>
       <c r="V38" s="8"/>
-      <c r="W38" s="8"/>
+      <c r="W38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="X38" s="8"/>
       <c r="Y38" s="8"/>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
       <c r="AC38" s="8"/>
-      <c r="AD38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
       <c r="AF38" s="8"/>
       <c r="AG38" s="8"/>
@@ -28988,13 +28988,13 @@
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
-      <c r="U39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U39" s="9"/>
       <c r="V39" s="9"/>
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
+      <c r="Y39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Z39" s="9"/>
       <c r="AA39" s="9"/>
       <c r="AB39" s="9"/>
@@ -29042,13 +29042,13 @@
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
-      <c r="Y40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Y40" s="8"/>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
       <c r="AB40" s="8"/>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
       <c r="AF40" s="8"/>
@@ -29087,7 +29087,9 @@
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
+      <c r="T41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U41" s="9"/>
       <c r="V41" s="9"/>
       <c r="W41" s="9"/>
@@ -29096,9 +29098,7 @@
       <c r="Z41" s="9"/>
       <c r="AA41" s="9"/>
       <c r="AB41" s="9"/>
-      <c r="AC41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AC41" s="9"/>
       <c r="AD41" s="9"/>
       <c r="AE41" s="9"/>
       <c r="AF41" s="9"/>
@@ -29141,16 +29141,16 @@
       <c r="U42" s="8"/>
       <c r="V42" s="8"/>
       <c r="W42" s="8"/>
-      <c r="X42" s="8"/>
+      <c r="X42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y42" s="8"/>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
       <c r="AD42" s="8"/>
-      <c r="AE42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE42" s="8"/>
       <c r="AF42" s="8"/>
       <c r="AG42" s="8"/>
       <c r="AH42" s="8"/>
@@ -29189,13 +29189,13 @@
       <c r="S43" s="9"/>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
-      <c r="V43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="V43" s="9"/>
       <c r="W43" s="9"/>
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
+      <c r="Z43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AA43" s="9"/>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
@@ -29243,13 +29243,13 @@
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
       <c r="Y44" s="8"/>
-      <c r="Z44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
       <c r="AC44" s="8"/>
-      <c r="AD44" s="8"/>
+      <c r="AD44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AE44" s="8"/>
       <c r="AF44" s="8"/>
       <c r="AG44" s="8"/>
@@ -29288,7 +29288,9 @@
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
       <c r="T45" s="9"/>
-      <c r="U45" s="9"/>
+      <c r="U45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V45" s="9"/>
       <c r="W45" s="9"/>
       <c r="X45" s="9"/>
@@ -29297,9 +29299,7 @@
       <c r="AA45" s="9"/>
       <c r="AB45" s="9"/>
       <c r="AC45" s="9"/>
-      <c r="AD45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD45" s="9"/>
       <c r="AE45" s="9"/>
       <c r="AF45" s="9"/>
       <c r="AG45" s="9"/>
@@ -29336,9 +29336,7 @@
       <c r="P46" s="8"/>
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
-      <c r="S46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S46" s="8"/>
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
       <c r="V46" s="8"/>
@@ -29355,7 +29353,9 @@
       <c r="AG46" s="8"/>
       <c r="AH46" s="8"/>
       <c r="AI46" s="8"/>
-      <c r="AJ46" s="8"/>
+      <c r="AJ46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AK46" s="8"/>
       <c r="AL46" s="8"/>
       <c r="AM46" s="8"/>
@@ -29390,13 +29390,13 @@
       <c r="T47" s="9"/>
       <c r="U47" s="9"/>
       <c r="V47" s="9"/>
-      <c r="W47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="W47" s="9"/>
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
       <c r="Z47" s="9"/>
-      <c r="AA47" s="9"/>
+      <c r="AA47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AB47" s="9"/>
       <c r="AC47" s="9"/>
       <c r="AD47" s="9"/>
@@ -29444,13 +29444,13 @@
       <c r="X48" s="8"/>
       <c r="Y48" s="8"/>
       <c r="Z48" s="8"/>
-      <c r="AA48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AA48" s="8"/>
       <c r="AB48" s="8"/>
       <c r="AC48" s="8"/>
       <c r="AD48" s="8"/>
-      <c r="AE48" s="8"/>
+      <c r="AE48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF48" s="8"/>
       <c r="AG48" s="8"/>
       <c r="AH48" s="8"/>
@@ -29489,16 +29489,16 @@
       <c r="S49" s="9"/>
       <c r="T49" s="9"/>
       <c r="U49" s="9"/>
-      <c r="V49" s="9"/>
+      <c r="V49" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="W49" s="9"/>
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
       <c r="Z49" s="9"/>
       <c r="AA49" s="9"/>
       <c r="AB49" s="9"/>
-      <c r="AC49" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AC49" s="9"/>
       <c r="AD49" s="9"/>
       <c r="AE49" s="9"/>
       <c r="AF49" s="9"/>
@@ -29537,13 +29537,13 @@
       <c r="Q50" s="8"/>
       <c r="R50" s="8"/>
       <c r="S50" s="8"/>
-      <c r="T50" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T50" s="8"/>
       <c r="U50" s="8"/>
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
-      <c r="X50" s="8"/>
+      <c r="X50" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y50" s="8"/>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
@@ -29591,13 +29591,13 @@
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
-      <c r="X51" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
       <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
+      <c r="AB51" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AC51" s="9"/>
       <c r="AD51" s="9"/>
       <c r="AE51" s="9"/>
@@ -29636,7 +29636,9 @@
       <c r="P52" s="8"/>
       <c r="Q52" s="8"/>
       <c r="R52" s="8"/>
-      <c r="S52" s="8"/>
+      <c r="S52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T52" s="8"/>
       <c r="U52" s="8"/>
       <c r="V52" s="8"/>
@@ -29646,9 +29648,7 @@
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
       <c r="AB52" s="8"/>
-      <c r="AC52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AC52" s="8"/>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
       <c r="AF52" s="8"/>
@@ -29691,11 +29691,11 @@
       <c r="U53" s="9"/>
       <c r="V53" s="9"/>
       <c r="W53" s="9"/>
-      <c r="X53" s="9" t="n">
+      <c r="X53" s="9"/>
+      <c r="Y53" s="9"/>
+      <c r="Z53" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
       <c r="AA53" s="9"/>
       <c r="AB53" s="9"/>
       <c r="AC53" s="9"/>
@@ -29736,11 +29736,11 @@
       <c r="P54" s="8"/>
       <c r="Q54" s="8"/>
       <c r="R54" s="8"/>
-      <c r="S54" s="8" t="n">
+      <c r="S54" s="8"/>
+      <c r="T54" s="8"/>
+      <c r="U54" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="T54" s="8"/>
-      <c r="U54" s="8"/>
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
@@ -29793,11 +29793,11 @@
       <c r="W55" s="9"/>
       <c r="X55" s="9"/>
       <c r="Y55" s="9"/>
-      <c r="Z55" s="9" t="n">
+      <c r="Z55" s="9"/>
+      <c r="AA55" s="9"/>
+      <c r="AB55" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
       <c r="AC55" s="9"/>
       <c r="AD55" s="9"/>
       <c r="AE55" s="9"/>
@@ -30301,10 +30301,10 @@
       <c r="AL65" s="9"/>
       <c r="AM65" s="9"/>
       <c r="AN65" s="9"/>
-      <c r="AO65" s="9"/>
-      <c r="AP65" s="9" t="n">
+      <c r="AO65" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AP65" s="9"/>
       <c r="AQ65" s="9"/>
     </row>
     <row r="66" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.25">
@@ -30447,11 +30447,11 @@
       <c r="AK68" s="8"/>
       <c r="AL68" s="8"/>
       <c r="AM68" s="8"/>
-      <c r="AN68" s="8"/>
+      <c r="AN68" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AO68" s="8"/>
-      <c r="AP68" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AP68" s="8"/>
       <c r="AQ68" s="8"/>
     </row>
     <row r="69" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -30546,10 +30546,10 @@
       <c r="AL70" s="8"/>
       <c r="AM70" s="8"/>
       <c r="AN70" s="8"/>
-      <c r="AO70" s="8" t="n">
+      <c r="AO70" s="8"/>
+      <c r="AP70" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP70" s="8"/>
       <c r="AQ70" s="8"/>
     </row>
     <row r="71" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -30643,11 +30643,11 @@
       <c r="AK72" s="8"/>
       <c r="AL72" s="8"/>
       <c r="AM72" s="8"/>
-      <c r="AN72" s="8" t="n">
+      <c r="AN72" s="8"/>
+      <c r="AO72" s="8"/>
+      <c r="AP72" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO72" s="8"/>
-      <c r="AP72" s="8"/>
       <c r="AQ72" s="8"/>
     </row>
     <row r="73" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -30692,10 +30692,10 @@
       <c r="AK73" s="9"/>
       <c r="AL73" s="9"/>
       <c r="AM73" s="9"/>
-      <c r="AN73" s="9" t="n">
+      <c r="AN73" s="9"/>
+      <c r="AO73" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AO73" s="9"/>
       <c r="AP73" s="9"/>
       <c r="AQ73" s="9"/>
     </row>
@@ -30742,10 +30742,10 @@
       <c r="AL74" s="8"/>
       <c r="AM74" s="8"/>
       <c r="AN74" s="8"/>
-      <c r="AO74" s="8" t="n">
+      <c r="AO74" s="8"/>
+      <c r="AP74" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP74" s="8"/>
       <c r="AQ74" s="8"/>
     </row>
     <row r="75" spans="1:43" ht="12" customHeight="1" ns2:dyDescent="0.3">
@@ -30937,10 +30937,10 @@
       <c r="AK78" s="8"/>
       <c r="AL78" s="8"/>
       <c r="AM78" s="8"/>
-      <c r="AN78" s="8"/>
-      <c r="AO78" s="8" t="n">
+      <c r="AN78" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO78" s="8"/>
       <c r="AP78" s="8"/>
       <c r="AQ78" s="8"/>
     </row>
@@ -30986,10 +30986,10 @@
       <c r="AK79" s="9"/>
       <c r="AL79" s="9"/>
       <c r="AM79" s="9"/>
-      <c r="AN79" s="9"/>
-      <c r="AO79" s="9" t="n">
+      <c r="AN79" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AO79" s="9"/>
       <c r="AP79" s="9"/>
       <c r="AQ79" s="9"/>
     </row>
@@ -31020,7 +31020,9 @@
       <c r="V80" s="8"/>
       <c r="W80" s="8"/>
       <c r="X80" s="8"/>
-      <c r="Y80" s="8"/>
+      <c r="Y80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Z80" s="8"/>
       <c r="AA80" s="8"/>
       <c r="AB80" s="8"/>
@@ -31030,9 +31032,7 @@
       <c r="AF80" s="8"/>
       <c r="AG80" s="8"/>
       <c r="AH80" s="8"/>
-      <c r="AI80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AI80" s="8"/>
       <c r="AJ80" s="8"/>
       <c r="AK80" s="8"/>
       <c r="AL80" s="8"/>
@@ -31063,7 +31063,9 @@
       <c r="P81" s="9"/>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
-      <c r="S81" s="9"/>
+      <c r="S81" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T81" s="9"/>
       <c r="U81" s="9"/>
       <c r="V81" s="9"/>
@@ -31074,9 +31076,7 @@
       <c r="AA81" s="9"/>
       <c r="AB81" s="9"/>
       <c r="AC81" s="9"/>
-      <c r="AD81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD81" s="9"/>
       <c r="AE81" s="9"/>
       <c r="AF81" s="9"/>
       <c r="AG81" s="9"/>
@@ -31118,11 +31118,11 @@
       <c r="V82" s="8"/>
       <c r="W82" s="8"/>
       <c r="X82" s="8"/>
-      <c r="Y82" s="8" t="n">
+      <c r="Y82" s="8"/>
+      <c r="Z82" s="8"/>
+      <c r="AA82" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="Z82" s="8"/>
-      <c r="AA82" s="8"/>
       <c r="AB82" s="8"/>
       <c r="AC82" s="8"/>
       <c r="AD82" s="8"/>
@@ -31161,9 +31161,7 @@
       <c r="P83" s="9"/>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
-      <c r="S83" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S83" s="9"/>
       <c r="T83" s="9"/>
       <c r="U83" s="9"/>
       <c r="V83" s="9"/>
@@ -31178,7 +31176,9 @@
       <c r="AE83" s="9"/>
       <c r="AF83" s="9"/>
       <c r="AG83" s="9"/>
-      <c r="AH83" s="9"/>
+      <c r="AH83" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AI83" s="9"/>
       <c r="AJ83" s="9"/>
       <c r="AK83" s="9"/>
